--- a/ref_file/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
+++ b/ref_file/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sjo\fem_temp\femm_ioniq5\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.업무폴더\2026년도업무\5.전략연구사업\IONIQ5_FEMM\ref_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12973" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975"/>
   </bookViews>
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
@@ -1255,58 +1255,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>135.66999999999999</c:v>
+                  <c:v>137.09</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134.16</c:v>
+                  <c:v>135.46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132.65</c:v>
+                  <c:v>133.68</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>131.16999999999999</c:v>
+                  <c:v>131.87</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>129.72</c:v>
+                  <c:v>130.08000000000001</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>128.32</c:v>
+                  <c:v>128.41</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>126.97</c:v>
+                  <c:v>127.11</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>125.69</c:v>
+                  <c:v>126.17</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>124.48</c:v>
+                  <c:v>125.46</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>123.36</c:v>
+                  <c:v>124.82</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>122.33</c:v>
+                  <c:v>124.19</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>121.41</c:v>
+                  <c:v>123.55</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>120.59</c:v>
+                  <c:v>122.72</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>119.89</c:v>
+                  <c:v>121.73</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>119.31</c:v>
+                  <c:v>120.64</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>118.85</c:v>
+                  <c:v>119.74</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>118.52</c:v>
+                  <c:v>118.99</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>118.32</c:v>
+                  <c:v>118.46</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>118.25</c:v>
@@ -1338,58 +1338,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>119.74</c:v>
+                  <c:v>114.9</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>109.84</c:v>
+                  <c:v>103.84</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>99.45</c:v>
+                  <c:v>93.31</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>88.64</c:v>
+                  <c:v>83.68</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>77.849999999999994</c:v>
+                  <c:v>74.709999999999994</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>67.31</c:v>
+                  <c:v>65.959999999999994</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>57.07</c:v>
+                  <c:v>57.22</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>47.15</c:v>
+                  <c:v>48.64</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>37.58</c:v>
+                  <c:v>40.340000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>28.34</c:v>
+                  <c:v>32.32</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>19.399999999999999</c:v>
+                  <c:v>24.07</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>10.32</c:v>
+                  <c:v>14.83</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.05</c:v>
+                  <c:v>4.91</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>-7.16</c:v>
+                  <c:v>-4.51</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>-14.17</c:v>
+                  <c:v>-12.93</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>-19.86</c:v>
+                  <c:v>-19.61</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>-23.78</c:v>
+                  <c:v>-23.99</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>-26.12</c:v>
+                  <c:v>-26.22</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>-26.92</c:v>
@@ -1408,11 +1408,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1370791856"/>
-        <c:axId val="1370791312"/>
+        <c:axId val="-32049312"/>
+        <c:axId val="-32059104"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1370791856"/>
+        <c:axId val="-32049312"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1455,7 +1455,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370791312"/>
+        <c:crossAx val="-32059104"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1463,7 +1463,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1370791312"/>
+        <c:axId val="-32059104"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1514,7 +1514,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370791856"/>
+        <c:crossAx val="-32049312"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1914,37 +1914,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>135.72</c:v>
+                  <c:v>137.31</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134.16</c:v>
+                  <c:v>135.46</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>132.65</c:v>
+                  <c:v>133.16</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>130.69999999999999</c:v>
+                  <c:v>130.76</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>127.54</c:v>
+                  <c:v>127.58</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>123.92</c:v>
+                  <c:v>123.53</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>120.71</c:v>
+                  <c:v>119.28</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>117.96</c:v>
+                  <c:v>114.99</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>115.28</c:v>
+                  <c:v>110.88</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>112.58</c:v>
+                  <c:v>107.18</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>109.84</c:v>
+                  <c:v>103.84</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2256,10 +2256,10 @@
                   <c:v>118.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100.85</c:v>
+                  <c:v>100.84</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>83.67</c:v>
+                  <c:v>83.66</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>67.14</c:v>
@@ -2296,11 +2296,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1370784240"/>
-        <c:axId val="1370786416"/>
+        <c:axId val="-32058560"/>
+        <c:axId val="-32055840"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1370784240"/>
+        <c:axId val="-32058560"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2343,7 +2343,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370786416"/>
+        <c:crossAx val="-32055840"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2351,7 +2351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1370786416"/>
+        <c:axId val="-32055840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2402,7 +2402,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370784240"/>
+        <c:crossAx val="-32058560"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3005,34 +3005,34 @@
                   <c:v>-0.01</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.53</c:v>
+                  <c:v>45.19</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>88.52</c:v>
+                  <c:v>89.22</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>127.42</c:v>
+                  <c:v>127.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>156.63999999999999</c:v>
+                  <c:v>154.22999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>178.99</c:v>
+                  <c:v>175.82</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>197</c:v>
+                  <c:v>194.62</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>211.64</c:v>
+                  <c:v>211.19</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>224.47</c:v>
+                  <c:v>225.12</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>236</c:v>
+                  <c:v>237.22</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>246.71</c:v>
+                  <c:v>248.25</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3114,37 +3114,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>-0.01</c:v>
+                  <c:v>-0.11</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.85</c:v>
+                  <c:v>3.96</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.71</c:v>
+                  <c:v>7.92</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.51</c:v>
+                  <c:v>11.69</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.2</c:v>
+                  <c:v>15.15</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18.88</c:v>
+                  <c:v>18.32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>22.41</c:v>
+                  <c:v>19.91</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.76</c:v>
+                  <c:v>20.97</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>28.98</c:v>
+                  <c:v>22.18</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>32.090000000000003</c:v>
+                  <c:v>23.27</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>35.119999999999997</c:v>
+                  <c:v>24.29</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3160,11 +3160,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1370790768"/>
-        <c:axId val="1370789136"/>
+        <c:axId val="-32055296"/>
+        <c:axId val="-32054752"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1370790768"/>
+        <c:axId val="-32055296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3207,7 +3207,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370789136"/>
+        <c:crossAx val="-32054752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3215,7 +3215,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1370789136"/>
+        <c:axId val="-32054752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3266,7 +3266,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370790768"/>
+        <c:crossAx val="-32055296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3786,61 +3786,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>246.71</c:v>
+                  <c:v>248.25</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>247.87</c:v>
+                  <c:v>245.16</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>248.12</c:v>
+                  <c:v>241.5</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>247.4</c:v>
+                  <c:v>237.62</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>245.65</c:v>
+                  <c:v>233.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>242.78</c:v>
+                  <c:v>227.93</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>238.63</c:v>
+                  <c:v>220.05</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>233.01</c:v>
+                  <c:v>210.05</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>225.89</c:v>
+                  <c:v>198.37</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>217.1</c:v>
+                  <c:v>185.13</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>206.28</c:v>
+                  <c:v>170.43</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>191.94</c:v>
+                  <c:v>154.07</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>173.47</c:v>
+                  <c:v>136.22</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>153</c:v>
+                  <c:v>116.61</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>129.41</c:v>
+                  <c:v>95</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>101.42</c:v>
+                  <c:v>71.92</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>69.41</c:v>
+                  <c:v>48.26</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>35.119999999999997</c:v>
+                  <c:v>24.29</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.03</c:v>
+                  <c:v>0.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4266,61 +4266,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>44.53</c:v>
+                  <c:v>45.19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>44.37</c:v>
+                  <c:v>43.94</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43.87</c:v>
+                  <c:v>42.79</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43.03</c:v>
+                  <c:v>42.02</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41.86</c:v>
+                  <c:v>41.33</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.369999999999997</c:v>
+                  <c:v>40.159999999999997</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38.57</c:v>
+                  <c:v>38.229999999999997</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>36.47</c:v>
+                  <c:v>35.94</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>34.090000000000003</c:v>
+                  <c:v>33.83</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>31.45</c:v>
+                  <c:v>31.85</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>28.57</c:v>
+                  <c:v>29.55</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>25.47</c:v>
+                  <c:v>26.29</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>22.19</c:v>
+                  <c:v>22.13</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>18.739999999999998</c:v>
+                  <c:v>17.8</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>15.16</c:v>
+                  <c:v>13.87</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>11.46</c:v>
+                  <c:v>10.53</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.68</c:v>
+                  <c:v>7.39</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.85</c:v>
+                  <c:v>3.96</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.01</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4336,11 +4336,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1370792400"/>
-        <c:axId val="1370781520"/>
+        <c:axId val="-256917184"/>
+        <c:axId val="-256919904"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1370792400"/>
+        <c:axId val="-256917184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4383,7 +4383,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370781520"/>
+        <c:crossAx val="-256919904"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4391,7 +4391,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1370781520"/>
+        <c:axId val="-256919904"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4442,7 +4442,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1370792400"/>
+        <c:crossAx val="-256917184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4948,11 +4948,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1369851312"/>
-        <c:axId val="1494581248"/>
+        <c:axId val="-256927520"/>
+        <c:axId val="-286198032"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1369851312"/>
+        <c:axId val="-256927520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4994,7 +4994,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1494581248"/>
+        <c:crossAx val="-286198032"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5002,7 +5002,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1494581248"/>
+        <c:axId val="-286198032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5053,7 +5053,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1369851312"/>
+        <c:crossAx val="-256927520"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5411,11 +5411,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1494593216"/>
-        <c:axId val="1494588320"/>
+        <c:axId val="-17300144"/>
+        <c:axId val="-17301232"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1494593216"/>
+        <c:axId val="-17300144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5457,7 +5457,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1494588320"/>
+        <c:crossAx val="-17301232"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5465,7 +5465,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1494588320"/>
+        <c:axId val="-17301232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5516,7 +5516,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1494593216"/>
+        <c:crossAx val="-17300144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9362,9 +9362,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
@@ -9478,41 +9478,41 @@
       <c r="N2" s="1">
         <v>90</v>
       </c>
-      <c r="O2" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P2" s="1">
-        <v>135.66999999999999</v>
-      </c>
-      <c r="Q2" s="1">
-        <v>135.6</v>
-      </c>
-      <c r="R2" s="1">
-        <v>134.72</v>
-      </c>
-      <c r="S2" s="1">
-        <v>132.47999999999999</v>
-      </c>
-      <c r="T2" s="1">
-        <v>129.72999999999999</v>
-      </c>
-      <c r="U2" s="1">
-        <v>127.23</v>
-      </c>
-      <c r="V2" s="1">
-        <v>125.26</v>
-      </c>
-      <c r="W2" s="1">
-        <v>123.41</v>
-      </c>
-      <c r="X2" s="1">
-        <v>121.57</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>119.74</v>
+      <c r="O2">
+        <v>137.38999999999999</v>
+      </c>
+      <c r="P2">
+        <v>137.09</v>
+      </c>
+      <c r="Q2">
+        <v>136.19999999999999</v>
+      </c>
+      <c r="R2">
+        <v>135.02000000000001</v>
+      </c>
+      <c r="S2">
+        <v>132.66999999999999</v>
+      </c>
+      <c r="T2">
+        <v>129.61000000000001</v>
+      </c>
+      <c r="U2">
+        <v>126.29</v>
+      </c>
+      <c r="V2">
+        <v>122.95</v>
+      </c>
+      <c r="W2">
+        <v>119.96</v>
+      </c>
+      <c r="X2">
+        <v>117.33</v>
+      </c>
+      <c r="Y2">
+        <v>114.9</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
@@ -9552,41 +9552,41 @@
       <c r="N3" s="1">
         <v>95</v>
       </c>
-      <c r="O3" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P3" s="1">
-        <v>134.16</v>
-      </c>
-      <c r="Q3" s="1">
-        <v>132.65</v>
-      </c>
-      <c r="R3" s="1">
-        <v>130.69999999999999</v>
-      </c>
-      <c r="S3" s="1">
-        <v>127.54</v>
-      </c>
-      <c r="T3" s="1">
-        <v>123.92</v>
-      </c>
-      <c r="U3" s="1">
-        <v>120.71</v>
-      </c>
-      <c r="V3" s="1">
-        <v>117.96</v>
-      </c>
-      <c r="W3" s="1">
-        <v>115.28</v>
-      </c>
-      <c r="X3" s="1">
-        <v>112.58</v>
-      </c>
-      <c r="Y3" s="1">
-        <v>109.84</v>
+      <c r="O3">
+        <v>137.31</v>
+      </c>
+      <c r="P3">
+        <v>135.46</v>
+      </c>
+      <c r="Q3">
+        <v>133.16</v>
+      </c>
+      <c r="R3">
+        <v>130.76</v>
+      </c>
+      <c r="S3">
+        <v>127.58</v>
+      </c>
+      <c r="T3">
+        <v>123.53</v>
+      </c>
+      <c r="U3">
+        <v>119.28</v>
+      </c>
+      <c r="V3">
+        <v>114.99</v>
+      </c>
+      <c r="W3">
+        <v>110.88</v>
+      </c>
+      <c r="X3">
+        <v>107.18</v>
+      </c>
+      <c r="Y3">
+        <v>103.84</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -9626,41 +9626,41 @@
       <c r="N4" s="1">
         <v>100</v>
       </c>
-      <c r="O4" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P4" s="1">
-        <v>132.65</v>
-      </c>
-      <c r="Q4" s="1">
-        <v>129.69999999999999</v>
-      </c>
-      <c r="R4" s="1">
-        <v>126.66</v>
-      </c>
-      <c r="S4" s="1">
+      <c r="O4">
+        <v>137.13999999999999</v>
+      </c>
+      <c r="P4">
+        <v>133.68</v>
+      </c>
+      <c r="Q4">
+        <v>130.03</v>
+      </c>
+      <c r="R4">
+        <v>126.47</v>
+      </c>
+      <c r="S4">
         <v>122.56</v>
       </c>
-      <c r="T4" s="1">
-        <v>118.04</v>
-      </c>
-      <c r="U4" s="1">
-        <v>114.03</v>
-      </c>
-      <c r="V4" s="1">
-        <v>110.44</v>
-      </c>
-      <c r="W4" s="1">
-        <v>106.87</v>
-      </c>
-      <c r="X4" s="1">
-        <v>103.2</v>
-      </c>
-      <c r="Y4" s="1">
-        <v>99.45</v>
+      <c r="T4">
+        <v>117.83</v>
+      </c>
+      <c r="U4">
+        <v>112.77</v>
+      </c>
+      <c r="V4">
+        <v>107.67</v>
+      </c>
+      <c r="W4">
+        <v>102.61</v>
+      </c>
+      <c r="X4">
+        <v>97.76</v>
+      </c>
+      <c r="Y4">
+        <v>93.31</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
@@ -9700,41 +9700,41 @@
       <c r="N5" s="1">
         <v>105</v>
       </c>
-      <c r="O5" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P5" s="1">
-        <v>131.16999999999999</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>126.78</v>
-      </c>
-      <c r="R5" s="1">
-        <v>122.6</v>
-      </c>
-      <c r="S5" s="1">
-        <v>117.56</v>
-      </c>
-      <c r="T5" s="1">
-        <v>112.08</v>
-      </c>
-      <c r="U5" s="1">
-        <v>107.15</v>
-      </c>
-      <c r="V5" s="1">
-        <v>102.61</v>
-      </c>
-      <c r="W5" s="1">
-        <v>98.08</v>
-      </c>
-      <c r="X5" s="1">
-        <v>93.42</v>
-      </c>
-      <c r="Y5" s="1">
-        <v>88.64</v>
+      <c r="O5">
+        <v>136.87</v>
+      </c>
+      <c r="P5">
+        <v>131.87</v>
+      </c>
+      <c r="Q5">
+        <v>126.9</v>
+      </c>
+      <c r="R5">
+        <v>122.25</v>
+      </c>
+      <c r="S5">
+        <v>117.45</v>
+      </c>
+      <c r="T5">
+        <v>112.11</v>
+      </c>
+      <c r="U5">
+        <v>106.48</v>
+      </c>
+      <c r="V5">
+        <v>100.71</v>
+      </c>
+      <c r="W5">
+        <v>94.92</v>
+      </c>
+      <c r="X5">
+        <v>89.18</v>
+      </c>
+      <c r="Y5">
+        <v>83.68</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
@@ -9774,41 +9774,41 @@
       <c r="N6" s="1">
         <v>110</v>
       </c>
-      <c r="O6" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P6" s="1">
-        <v>129.72</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>123.91</v>
-      </c>
-      <c r="R6" s="1">
-        <v>118.53</v>
-      </c>
-      <c r="S6" s="1">
-        <v>112.59</v>
-      </c>
-      <c r="T6" s="1">
-        <v>106.16</v>
-      </c>
-      <c r="U6" s="1">
-        <v>100.24</v>
-      </c>
-      <c r="V6" s="1">
-        <v>94.71</v>
-      </c>
-      <c r="W6" s="1">
-        <v>89.2</v>
-      </c>
-      <c r="X6" s="1">
-        <v>83.6</v>
-      </c>
-      <c r="Y6" s="1">
-        <v>77.849999999999994</v>
+      <c r="O6">
+        <v>136.47</v>
+      </c>
+      <c r="P6">
+        <v>130.08000000000001</v>
+      </c>
+      <c r="Q6">
+        <v>123.9</v>
+      </c>
+      <c r="R6">
+        <v>118.31</v>
+      </c>
+      <c r="S6">
+        <v>112.4</v>
+      </c>
+      <c r="T6">
+        <v>106.36</v>
+      </c>
+      <c r="U6">
+        <v>100.19</v>
+      </c>
+      <c r="V6">
+        <v>93.9</v>
+      </c>
+      <c r="W6">
+        <v>87.53</v>
+      </c>
+      <c r="X6">
+        <v>81.09</v>
+      </c>
+      <c r="Y6">
+        <v>74.709999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
@@ -9848,41 +9848,41 @@
       <c r="N7" s="1">
         <v>115</v>
       </c>
-      <c r="O7" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P7" s="1">
-        <v>128.32</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>121.12</v>
-      </c>
-      <c r="R7" s="1">
-        <v>114.48</v>
-      </c>
-      <c r="S7" s="1">
-        <v>107.68</v>
-      </c>
-      <c r="T7" s="1">
-        <v>100.36</v>
-      </c>
-      <c r="U7" s="1">
-        <v>93.45</v>
-      </c>
-      <c r="V7" s="1">
-        <v>86.93</v>
-      </c>
-      <c r="W7" s="1">
-        <v>80.47</v>
-      </c>
-      <c r="X7" s="1">
-        <v>73.94</v>
-      </c>
-      <c r="Y7" s="1">
-        <v>67.31</v>
+      <c r="O7">
+        <v>136.04</v>
+      </c>
+      <c r="P7">
+        <v>128.41</v>
+      </c>
+      <c r="Q7">
+        <v>121.07</v>
+      </c>
+      <c r="R7">
+        <v>114.44</v>
+      </c>
+      <c r="S7">
+        <v>107.55</v>
+      </c>
+      <c r="T7">
+        <v>100.44</v>
+      </c>
+      <c r="U7">
+        <v>93.6</v>
+      </c>
+      <c r="V7">
+        <v>86.78</v>
+      </c>
+      <c r="W7">
+        <v>79.900000000000006</v>
+      </c>
+      <c r="X7">
+        <v>72.959999999999994</v>
+      </c>
+      <c r="Y7">
+        <v>65.959999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
@@ -9922,41 +9922,41 @@
       <c r="N8" s="1">
         <v>120</v>
       </c>
-      <c r="O8" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P8" s="1">
-        <v>126.97</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>118.43</v>
-      </c>
-      <c r="R8" s="1">
-        <v>110.52</v>
-      </c>
-      <c r="S8" s="1">
-        <v>102.82</v>
-      </c>
-      <c r="T8" s="1">
-        <v>94.68</v>
-      </c>
-      <c r="U8" s="1">
-        <v>86.84</v>
-      </c>
-      <c r="V8" s="1">
-        <v>79.37</v>
-      </c>
-      <c r="W8" s="1">
-        <v>71.97</v>
-      </c>
-      <c r="X8" s="1">
-        <v>64.540000000000006</v>
-      </c>
-      <c r="Y8" s="1">
-        <v>57.07</v>
+      <c r="O8">
+        <v>135.86000000000001</v>
+      </c>
+      <c r="P8">
+        <v>127.11</v>
+      </c>
+      <c r="Q8">
+        <v>118.58</v>
+      </c>
+      <c r="R8">
+        <v>110.7</v>
+      </c>
+      <c r="S8">
+        <v>103.02</v>
+      </c>
+      <c r="T8">
+        <v>94.89</v>
+      </c>
+      <c r="U8">
+        <v>87.03</v>
+      </c>
+      <c r="V8">
+        <v>79.540000000000006</v>
+      </c>
+      <c r="W8">
+        <v>72.14</v>
+      </c>
+      <c r="X8">
+        <v>64.709999999999994</v>
+      </c>
+      <c r="Y8">
+        <v>57.22</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>125</v>
       </c>
@@ -9996,41 +9996,41 @@
       <c r="N9" s="1">
         <v>125</v>
       </c>
-      <c r="O9" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P9" s="1">
-        <v>125.69</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>115.86</v>
-      </c>
-      <c r="R9" s="1">
-        <v>106.7</v>
-      </c>
-      <c r="S9" s="1">
-        <v>97.97</v>
-      </c>
-      <c r="T9" s="1">
-        <v>89.12</v>
-      </c>
-      <c r="U9" s="1">
-        <v>80.41</v>
-      </c>
-      <c r="V9" s="1">
-        <v>72.05</v>
-      </c>
-      <c r="W9" s="1">
-        <v>63.76</v>
-      </c>
-      <c r="X9" s="1">
-        <v>55.46</v>
-      </c>
-      <c r="Y9" s="1">
-        <v>47.15</v>
+      <c r="O9">
+        <v>136.01</v>
+      </c>
+      <c r="P9">
+        <v>126.17</v>
+      </c>
+      <c r="Q9">
+        <v>116.54</v>
+      </c>
+      <c r="R9">
+        <v>107.37</v>
+      </c>
+      <c r="S9">
+        <v>98.78</v>
+      </c>
+      <c r="T9">
+        <v>90.05</v>
+      </c>
+      <c r="U9">
+        <v>81.06</v>
+      </c>
+      <c r="V9">
+        <v>72.58</v>
+      </c>
+      <c r="W9">
+        <v>64.52</v>
+      </c>
+      <c r="X9">
+        <v>56.58</v>
+      </c>
+      <c r="Y9">
+        <v>48.64</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>130</v>
       </c>
@@ -10070,41 +10070,41 @@
       <c r="N10" s="1">
         <v>130</v>
       </c>
-      <c r="O10" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P10" s="1">
-        <v>124.48</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>113.44</v>
-      </c>
-      <c r="R10" s="1">
-        <v>103.06</v>
-      </c>
-      <c r="S10" s="1">
-        <v>93.22</v>
-      </c>
-      <c r="T10" s="1">
-        <v>83.59</v>
-      </c>
-      <c r="U10" s="1">
-        <v>74.099999999999994</v>
-      </c>
-      <c r="V10" s="1">
-        <v>64.94</v>
-      </c>
-      <c r="W10" s="1">
-        <v>55.83</v>
-      </c>
-      <c r="X10" s="1">
-        <v>46.71</v>
-      </c>
-      <c r="Y10" s="1">
-        <v>37.58</v>
+      <c r="O10">
+        <v>136.43</v>
+      </c>
+      <c r="P10">
+        <v>125.46</v>
+      </c>
+      <c r="Q10">
+        <v>114.75</v>
+      </c>
+      <c r="R10">
+        <v>104.56</v>
+      </c>
+      <c r="S10">
+        <v>94.88</v>
+      </c>
+      <c r="T10">
+        <v>85.54</v>
+      </c>
+      <c r="U10">
+        <v>75.95</v>
+      </c>
+      <c r="V10">
+        <v>66.349999999999994</v>
+      </c>
+      <c r="W10">
+        <v>57.35</v>
+      </c>
+      <c r="X10">
+        <v>48.78</v>
+      </c>
+      <c r="Y10">
+        <v>40.340000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>135</v>
       </c>
@@ -10144,41 +10144,41 @@
       <c r="N11" s="1">
         <v>135</v>
       </c>
-      <c r="O11" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P11" s="1">
-        <v>123.36</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>111.18</v>
-      </c>
-      <c r="R11" s="1">
-        <v>99.65</v>
-      </c>
-      <c r="S11" s="1">
-        <v>88.68</v>
-      </c>
-      <c r="T11" s="1">
-        <v>78.06</v>
-      </c>
-      <c r="U11" s="1">
-        <v>67.77</v>
-      </c>
-      <c r="V11" s="1">
-        <v>57.91</v>
-      </c>
-      <c r="W11" s="1">
-        <v>48.09</v>
-      </c>
-      <c r="X11" s="1">
-        <v>38.22</v>
-      </c>
-      <c r="Y11" s="1">
-        <v>28.34</v>
+      <c r="O11">
+        <v>136.81</v>
+      </c>
+      <c r="P11">
+        <v>124.82</v>
+      </c>
+      <c r="Q11">
+        <v>113.14</v>
+      </c>
+      <c r="R11">
+        <v>102.09</v>
+      </c>
+      <c r="S11">
+        <v>91.55</v>
+      </c>
+      <c r="T11">
+        <v>81.400000000000006</v>
+      </c>
+      <c r="U11">
+        <v>71.2</v>
+      </c>
+      <c r="V11">
+        <v>60.93</v>
+      </c>
+      <c r="W11">
+        <v>50.8</v>
+      </c>
+      <c r="X11">
+        <v>41.35</v>
+      </c>
+      <c r="Y11">
+        <v>32.32</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>140</v>
       </c>
@@ -10218,41 +10218,41 @@
       <c r="N12" s="1">
         <v>140</v>
       </c>
-      <c r="O12" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P12" s="1">
-        <v>122.33</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>109.1</v>
-      </c>
-      <c r="R12" s="1">
-        <v>96.5</v>
-      </c>
-      <c r="S12" s="1">
-        <v>84.44</v>
-      </c>
-      <c r="T12" s="1">
-        <v>72.75</v>
-      </c>
-      <c r="U12" s="1">
-        <v>61.44</v>
-      </c>
-      <c r="V12" s="1">
-        <v>50.73</v>
-      </c>
-      <c r="W12" s="1">
-        <v>40.340000000000003</v>
-      </c>
-      <c r="X12" s="1">
-        <v>29.9</v>
-      </c>
-      <c r="Y12" s="1">
-        <v>19.399999999999999</v>
+      <c r="O12">
+        <v>137.05000000000001</v>
+      </c>
+      <c r="P12">
+        <v>124.19</v>
+      </c>
+      <c r="Q12">
+        <v>111.69</v>
+      </c>
+      <c r="R12">
+        <v>99.82</v>
+      </c>
+      <c r="S12">
+        <v>88.45</v>
+      </c>
+      <c r="T12">
+        <v>77.36</v>
+      </c>
+      <c r="U12">
+        <v>66.349999999999994</v>
+      </c>
+      <c r="V12">
+        <v>55.38</v>
+      </c>
+      <c r="W12">
+        <v>44.52</v>
+      </c>
+      <c r="X12">
+        <v>33.93</v>
+      </c>
+      <c r="Y12">
+        <v>24.07</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>145</v>
       </c>
@@ -10292,41 +10292,41 @@
       <c r="N13" s="1">
         <v>145</v>
       </c>
-      <c r="O13" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P13" s="1">
-        <v>121.41</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>107.22</v>
-      </c>
-      <c r="R13" s="1">
-        <v>93.62</v>
-      </c>
-      <c r="S13" s="1">
-        <v>80.569999999999993</v>
-      </c>
-      <c r="T13" s="1">
-        <v>67.87</v>
-      </c>
-      <c r="U13" s="1">
-        <v>55.51</v>
-      </c>
-      <c r="V13" s="1">
-        <v>43.66</v>
-      </c>
-      <c r="W13" s="1">
-        <v>32.380000000000003</v>
-      </c>
-      <c r="X13" s="1">
-        <v>21.3</v>
-      </c>
-      <c r="Y13" s="1">
-        <v>10.32</v>
+      <c r="O13">
+        <v>137.22</v>
+      </c>
+      <c r="P13">
+        <v>123.55</v>
+      </c>
+      <c r="Q13">
+        <v>110.19</v>
+      </c>
+      <c r="R13">
+        <v>97.34</v>
+      </c>
+      <c r="S13">
+        <v>84.99</v>
+      </c>
+      <c r="T13">
+        <v>72.89</v>
+      </c>
+      <c r="U13">
+        <v>60.87</v>
+      </c>
+      <c r="V13">
+        <v>49.01</v>
+      </c>
+      <c r="W13">
+        <v>37.33</v>
+      </c>
+      <c r="X13">
+        <v>25.88</v>
+      </c>
+      <c r="Y13">
+        <v>14.83</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>150</v>
       </c>
@@ -10366,41 +10366,41 @@
       <c r="N14" s="1">
         <v>150</v>
       </c>
-      <c r="O14" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P14" s="1">
-        <v>120.59</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>105.56</v>
-      </c>
-      <c r="R14" s="1">
-        <v>91.07</v>
-      </c>
-      <c r="S14" s="1">
-        <v>77.11</v>
-      </c>
-      <c r="T14" s="1">
-        <v>63.49</v>
-      </c>
-      <c r="U14" s="1">
-        <v>50.18</v>
-      </c>
-      <c r="V14" s="1">
-        <v>37.25</v>
-      </c>
-      <c r="W14" s="1">
-        <v>24.87</v>
-      </c>
-      <c r="X14" s="1">
-        <v>12.85</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>1.05</v>
+      <c r="O14">
+        <v>137.30000000000001</v>
+      </c>
+      <c r="P14">
+        <v>122.72</v>
+      </c>
+      <c r="Q14">
+        <v>108.35</v>
+      </c>
+      <c r="R14">
+        <v>94.36</v>
+      </c>
+      <c r="S14">
+        <v>80.87</v>
+      </c>
+      <c r="T14">
+        <v>67.7</v>
+      </c>
+      <c r="U14">
+        <v>54.72</v>
+      </c>
+      <c r="V14">
+        <v>41.9</v>
+      </c>
+      <c r="W14">
+        <v>29.32</v>
+      </c>
+      <c r="X14">
+        <v>16.98</v>
+      </c>
+      <c r="Y14">
+        <v>4.91</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>155</v>
       </c>
@@ -10440,41 +10440,41 @@
       <c r="N15" s="1">
         <v>155</v>
       </c>
-      <c r="O15" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P15" s="1">
-        <v>119.89</v>
-      </c>
-      <c r="Q15" s="1">
-        <v>104.14</v>
-      </c>
-      <c r="R15" s="1">
-        <v>88.86</v>
-      </c>
-      <c r="S15" s="1">
-        <v>74.099999999999994</v>
-      </c>
-      <c r="T15" s="1">
-        <v>59.69</v>
-      </c>
-      <c r="U15" s="1">
-        <v>45.55</v>
-      </c>
-      <c r="V15" s="1">
-        <v>31.71</v>
-      </c>
-      <c r="W15" s="1">
-        <v>18.309999999999999</v>
-      </c>
-      <c r="X15" s="1">
-        <v>5.41</v>
-      </c>
-      <c r="Y15" s="1">
-        <v>-7.16</v>
+      <c r="O15">
+        <v>137.18</v>
+      </c>
+      <c r="P15">
+        <v>121.73</v>
+      </c>
+      <c r="Q15">
+        <v>106.37</v>
+      </c>
+      <c r="R15">
+        <v>91.33</v>
+      </c>
+      <c r="S15">
+        <v>76.66</v>
+      </c>
+      <c r="T15">
+        <v>62.4</v>
+      </c>
+      <c r="U15">
+        <v>48.49</v>
+      </c>
+      <c r="V15">
+        <v>34.86</v>
+      </c>
+      <c r="W15">
+        <v>21.42</v>
+      </c>
+      <c r="X15">
+        <v>8.27</v>
+      </c>
+      <c r="Y15">
+        <v>-4.51</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>160</v>
       </c>
@@ -10514,41 +10514,41 @@
       <c r="N16" s="1">
         <v>160</v>
       </c>
-      <c r="O16" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P16" s="1">
-        <v>119.31</v>
-      </c>
-      <c r="Q16" s="1">
-        <v>102.96</v>
-      </c>
-      <c r="R16" s="1">
-        <v>87.02</v>
-      </c>
-      <c r="S16" s="1">
-        <v>71.58</v>
-      </c>
-      <c r="T16" s="1">
-        <v>56.5</v>
-      </c>
-      <c r="U16" s="1">
-        <v>41.75</v>
-      </c>
-      <c r="V16" s="1">
-        <v>27.28</v>
-      </c>
-      <c r="W16" s="1">
-        <v>13.06</v>
-      </c>
-      <c r="X16" s="1">
-        <v>-0.8</v>
-      </c>
-      <c r="Y16" s="1">
-        <v>-14.17</v>
+      <c r="O16">
+        <v>136.99</v>
+      </c>
+      <c r="P16">
+        <v>120.64</v>
+      </c>
+      <c r="Q16">
+        <v>104.37</v>
+      </c>
+      <c r="R16">
+        <v>88.44</v>
+      </c>
+      <c r="S16">
+        <v>72.92</v>
+      </c>
+      <c r="T16">
+        <v>57.69</v>
+      </c>
+      <c r="U16">
+        <v>42.84</v>
+      </c>
+      <c r="V16">
+        <v>28.39</v>
+      </c>
+      <c r="W16">
+        <v>14.28</v>
+      </c>
+      <c r="X16">
+        <v>0.49</v>
+      </c>
+      <c r="Y16">
+        <v>-12.93</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>165</v>
       </c>
@@ -10588,41 +10588,41 @@
       <c r="N17" s="1">
         <v>165</v>
       </c>
-      <c r="O17" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P17" s="1">
-        <v>118.85</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>102.04</v>
-      </c>
-      <c r="R17" s="1">
-        <v>85.57</v>
-      </c>
-      <c r="S17" s="1">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="T17" s="1">
-        <v>54.05</v>
-      </c>
-      <c r="U17" s="1">
-        <v>38.840000000000003</v>
-      </c>
-      <c r="V17" s="1">
-        <v>23.85</v>
-      </c>
-      <c r="W17" s="1">
-        <v>9.0299999999999994</v>
-      </c>
-      <c r="X17" s="1">
-        <v>-5.58</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>-19.86</v>
+      <c r="O17">
+        <v>136.71</v>
+      </c>
+      <c r="P17">
+        <v>119.74</v>
+      </c>
+      <c r="Q17">
+        <v>102.79</v>
+      </c>
+      <c r="R17">
+        <v>86.16</v>
+      </c>
+      <c r="S17">
+        <v>70.040000000000006</v>
+      </c>
+      <c r="T17">
+        <v>54.25</v>
+      </c>
+      <c r="U17">
+        <v>38.74</v>
+      </c>
+      <c r="V17">
+        <v>23.55</v>
+      </c>
+      <c r="W17">
+        <v>8.8000000000000007</v>
+      </c>
+      <c r="X17">
+        <v>-5.59</v>
+      </c>
+      <c r="Y17">
+        <v>-19.61</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>170</v>
       </c>
@@ -10662,41 +10662,41 @@
       <c r="N18" s="1">
         <v>170</v>
       </c>
-      <c r="O18" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P18" s="1">
-        <v>118.52</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>101.38</v>
-      </c>
-      <c r="R18" s="1">
-        <v>84.52</v>
-      </c>
-      <c r="S18" s="1">
-        <v>68.2</v>
-      </c>
-      <c r="T18" s="1">
-        <v>52.34</v>
-      </c>
-      <c r="U18" s="1">
-        <v>36.76</v>
-      </c>
-      <c r="V18" s="1">
-        <v>21.37</v>
-      </c>
-      <c r="W18" s="1">
-        <v>6.14</v>
-      </c>
-      <c r="X18" s="1">
-        <v>-8.93</v>
-      </c>
-      <c r="Y18" s="1">
-        <v>-23.78</v>
+      <c r="O18">
+        <v>136.31</v>
+      </c>
+      <c r="P18">
+        <v>118.99</v>
+      </c>
+      <c r="Q18">
+        <v>101.72</v>
+      </c>
+      <c r="R18">
+        <v>84.76</v>
+      </c>
+      <c r="S18">
+        <v>68.28</v>
+      </c>
+      <c r="T18">
+        <v>52.13</v>
+      </c>
+      <c r="U18">
+        <v>36.340000000000003</v>
+      </c>
+      <c r="V18">
+        <v>20.87</v>
+      </c>
+      <c r="W18">
+        <v>5.64</v>
+      </c>
+      <c r="X18">
+        <v>-9.32</v>
+      </c>
+      <c r="Y18">
+        <v>-23.99</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>175</v>
       </c>
@@ -10736,41 +10736,41 @@
       <c r="N19" s="1">
         <v>175</v>
       </c>
-      <c r="O19" s="1">
-        <v>135.72</v>
-      </c>
-      <c r="P19" s="1">
-        <v>118.32</v>
-      </c>
-      <c r="Q19" s="1">
-        <v>100.98</v>
-      </c>
-      <c r="R19" s="1">
-        <v>83.89</v>
-      </c>
-      <c r="S19" s="1">
-        <v>67.400000000000006</v>
-      </c>
-      <c r="T19" s="1">
-        <v>51.32</v>
-      </c>
-      <c r="U19" s="1">
-        <v>35.49</v>
-      </c>
-      <c r="V19" s="1">
-        <v>19.84</v>
-      </c>
-      <c r="W19" s="1">
-        <v>4.3499999999999996</v>
-      </c>
-      <c r="X19" s="1">
-        <v>-11</v>
-      </c>
-      <c r="Y19" s="1">
-        <v>-26.12</v>
+      <c r="O19">
+        <v>135.88999999999999</v>
+      </c>
+      <c r="P19">
+        <v>118.46</v>
+      </c>
+      <c r="Q19">
+        <v>101.09</v>
+      </c>
+      <c r="R19">
+        <v>83.99</v>
+      </c>
+      <c r="S19">
+        <v>67.38</v>
+      </c>
+      <c r="T19">
+        <v>51.21</v>
+      </c>
+      <c r="U19">
+        <v>35.340000000000003</v>
+      </c>
+      <c r="V19">
+        <v>19.670000000000002</v>
+      </c>
+      <c r="W19">
+        <v>4.18</v>
+      </c>
+      <c r="X19">
+        <v>-11.15</v>
+      </c>
+      <c r="Y19">
+        <v>-26.22</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>180</v>
       </c>
@@ -10810,41 +10810,41 @@
       <c r="N20" s="1">
         <v>180</v>
       </c>
-      <c r="O20" s="1">
+      <c r="O20">
         <v>135.72</v>
       </c>
-      <c r="P20" s="1">
+      <c r="P20">
         <v>118.25</v>
       </c>
-      <c r="Q20" s="1">
-        <v>100.85</v>
-      </c>
-      <c r="R20" s="1">
-        <v>83.67</v>
-      </c>
-      <c r="S20" s="1">
+      <c r="Q20">
+        <v>100.84</v>
+      </c>
+      <c r="R20">
+        <v>83.66</v>
+      </c>
+      <c r="S20">
         <v>67.14</v>
       </c>
-      <c r="T20" s="1">
+      <c r="T20">
         <v>50.99</v>
       </c>
-      <c r="U20" s="1">
+      <c r="U20">
         <v>35.049999999999997</v>
       </c>
-      <c r="V20" s="1">
+      <c r="V20">
         <v>19.29</v>
       </c>
-      <c r="W20" s="1">
+      <c r="W20">
         <v>3.71</v>
       </c>
-      <c r="X20" s="1">
+      <c r="X20">
         <v>-11.71</v>
       </c>
-      <c r="Y20" s="1">
+      <c r="Y20">
         <v>-26.92</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>90</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>122.91</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>95</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>113.96</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>100</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>105.1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>105</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>95.79</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>110</v>
       </c>
@@ -11069,7 +11069,7 @@
         <v>86.04</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>115</v>
       </c>
@@ -11107,7 +11107,7 @@
         <v>76.37</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>120</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>66.78</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>125</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>130</v>
       </c>
@@ -11221,7 +11221,7 @@
         <v>47.53</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>135</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>37.119999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>140</v>
       </c>
@@ -11297,7 +11297,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>145</v>
       </c>
@@ -11335,7 +11335,7 @@
         <v>18.66</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>150</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>155</v>
       </c>
@@ -11411,7 +11411,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>160</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>-7.37</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>165</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>-14.14</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>170</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>-19.260000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>175</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>-22.67</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>180</v>
       </c>
@@ -11611,9 +11611,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -11687,7 +11687,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>90</v>
       </c>
@@ -11727,41 +11727,41 @@
       <c r="N2" s="2">
         <v>90</v>
       </c>
-      <c r="O2" s="2">
+      <c r="O2">
         <v>-0.01</v>
       </c>
-      <c r="P2" s="2">
-        <v>44.53</v>
-      </c>
-      <c r="Q2" s="2">
-        <v>88.52</v>
-      </c>
-      <c r="R2" s="2">
-        <v>127.42</v>
-      </c>
-      <c r="S2" s="2">
-        <v>156.63999999999999</v>
-      </c>
-      <c r="T2" s="2">
-        <v>178.99</v>
-      </c>
-      <c r="U2" s="2">
-        <v>197</v>
-      </c>
-      <c r="V2" s="2">
-        <v>211.64</v>
-      </c>
-      <c r="W2" s="2">
-        <v>224.47</v>
-      </c>
-      <c r="X2" s="2">
-        <v>236</v>
-      </c>
-      <c r="Y2" s="2">
-        <v>246.71</v>
+      <c r="P2">
+        <v>45.19</v>
+      </c>
+      <c r="Q2">
+        <v>89.22</v>
+      </c>
+      <c r="R2">
+        <v>127.04</v>
+      </c>
+      <c r="S2">
+        <v>154.22999999999999</v>
+      </c>
+      <c r="T2">
+        <v>175.82</v>
+      </c>
+      <c r="U2">
+        <v>194.62</v>
+      </c>
+      <c r="V2">
+        <v>211.19</v>
+      </c>
+      <c r="W2">
+        <v>225.12</v>
+      </c>
+      <c r="X2">
+        <v>237.22</v>
+      </c>
+      <c r="Y2">
+        <v>248.25</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>95</v>
       </c>
@@ -11801,41 +11801,41 @@
       <c r="N3" s="2">
         <v>95</v>
       </c>
-      <c r="O3" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P3" s="2">
-        <v>44.37</v>
-      </c>
-      <c r="Q3" s="2">
-        <v>88.2</v>
-      </c>
-      <c r="R3" s="2">
-        <v>127.44</v>
-      </c>
-      <c r="S3" s="2">
-        <v>157.1</v>
-      </c>
-      <c r="T3" s="2">
-        <v>179.74</v>
-      </c>
-      <c r="U3" s="2">
-        <v>197.65</v>
-      </c>
-      <c r="V3" s="2">
-        <v>212.34</v>
-      </c>
-      <c r="W3" s="2">
-        <v>225.31</v>
-      </c>
-      <c r="X3" s="2">
-        <v>237.01</v>
-      </c>
-      <c r="Y3" s="2">
-        <v>247.87</v>
+      <c r="O3">
+        <v>-0.95</v>
+      </c>
+      <c r="P3">
+        <v>43.94</v>
+      </c>
+      <c r="Q3">
+        <v>88.02</v>
+      </c>
+      <c r="R3">
+        <v>125.78</v>
+      </c>
+      <c r="S3">
+        <v>152.97</v>
+      </c>
+      <c r="T3">
+        <v>174.86</v>
+      </c>
+      <c r="U3">
+        <v>193.53</v>
+      </c>
+      <c r="V3">
+        <v>209.09</v>
+      </c>
+      <c r="W3">
+        <v>222.28</v>
+      </c>
+      <c r="X3">
+        <v>234.13</v>
+      </c>
+      <c r="Y3">
+        <v>245.16</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>100</v>
       </c>
@@ -11875,41 +11875,41 @@
       <c r="N4" s="2">
         <v>100</v>
       </c>
-      <c r="O4" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P4" s="2">
-        <v>43.87</v>
-      </c>
-      <c r="Q4" s="2">
-        <v>87.2</v>
-      </c>
-      <c r="R4" s="2">
-        <v>126.53</v>
-      </c>
-      <c r="S4" s="2">
-        <v>156.63999999999999</v>
-      </c>
-      <c r="T4" s="2">
-        <v>179.55</v>
-      </c>
-      <c r="U4" s="2">
-        <v>197.39</v>
-      </c>
-      <c r="V4" s="2">
-        <v>212.13</v>
-      </c>
-      <c r="W4" s="2">
-        <v>225.27</v>
-      </c>
-      <c r="X4" s="2">
-        <v>237.12</v>
-      </c>
-      <c r="Y4" s="2">
-        <v>248.12</v>
+      <c r="O4">
+        <v>-1.35</v>
+      </c>
+      <c r="P4">
+        <v>42.79</v>
+      </c>
+      <c r="Q4">
+        <v>86.49</v>
+      </c>
+      <c r="R4">
+        <v>123.83</v>
+      </c>
+      <c r="S4">
+        <v>151.05000000000001</v>
+      </c>
+      <c r="T4">
+        <v>172.9</v>
+      </c>
+      <c r="U4">
+        <v>190.71</v>
+      </c>
+      <c r="V4">
+        <v>205.5</v>
+      </c>
+      <c r="W4">
+        <v>218.45</v>
+      </c>
+      <c r="X4">
+        <v>230.34</v>
+      </c>
+      <c r="Y4">
+        <v>241.5</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>105</v>
       </c>
@@ -11949,41 +11949,41 @@
       <c r="N5" s="2">
         <v>105</v>
       </c>
-      <c r="O5" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P5" s="2">
-        <v>43.03</v>
-      </c>
-      <c r="Q5" s="2">
-        <v>85.55</v>
-      </c>
-      <c r="R5" s="2">
-        <v>124.64</v>
-      </c>
-      <c r="S5" s="2">
-        <v>155.24</v>
-      </c>
-      <c r="T5" s="2">
-        <v>178.39</v>
-      </c>
-      <c r="U5" s="2">
-        <v>196.2</v>
-      </c>
-      <c r="V5" s="2">
-        <v>210.96</v>
-      </c>
-      <c r="W5" s="2">
-        <v>224.23</v>
-      </c>
-      <c r="X5" s="2">
-        <v>236.28</v>
-      </c>
-      <c r="Y5" s="2">
-        <v>247.4</v>
+      <c r="O5">
+        <v>-1.0900000000000001</v>
+      </c>
+      <c r="P5">
+        <v>42.02</v>
+      </c>
+      <c r="Q5">
+        <v>84.69</v>
+      </c>
+      <c r="R5">
+        <v>121.28</v>
+      </c>
+      <c r="S5">
+        <v>148.35</v>
+      </c>
+      <c r="T5">
+        <v>169.51</v>
+      </c>
+      <c r="U5">
+        <v>186.62</v>
+      </c>
+      <c r="V5">
+        <v>201.12</v>
+      </c>
+      <c r="W5">
+        <v>214.17</v>
+      </c>
+      <c r="X5">
+        <v>226.26</v>
+      </c>
+      <c r="Y5">
+        <v>237.62</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>110</v>
       </c>
@@ -12023,41 +12023,41 @@
       <c r="N6" s="2">
         <v>110</v>
       </c>
-      <c r="O6" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P6" s="2">
-        <v>41.86</v>
-      </c>
-      <c r="Q6" s="2">
-        <v>83.25</v>
-      </c>
-      <c r="R6" s="2">
-        <v>121.71</v>
-      </c>
-      <c r="S6" s="2">
-        <v>152.81</v>
-      </c>
-      <c r="T6" s="2">
-        <v>176.26</v>
-      </c>
-      <c r="U6" s="2">
-        <v>194.09</v>
-      </c>
-      <c r="V6" s="2">
-        <v>208.84</v>
-      </c>
-      <c r="W6" s="2">
-        <v>222.16</v>
-      </c>
-      <c r="X6" s="2">
-        <v>234.4</v>
-      </c>
-      <c r="Y6" s="2">
-        <v>245.65</v>
+      <c r="O6">
+        <v>-0.53</v>
+      </c>
+      <c r="P6">
+        <v>41.33</v>
+      </c>
+      <c r="Q6">
+        <v>82.59</v>
+      </c>
+      <c r="R6">
+        <v>118.16</v>
+      </c>
+      <c r="S6">
+        <v>144.78</v>
+      </c>
+      <c r="T6">
+        <v>165.15</v>
+      </c>
+      <c r="U6">
+        <v>181.95</v>
+      </c>
+      <c r="V6">
+        <v>196.47</v>
+      </c>
+      <c r="W6">
+        <v>209.66</v>
+      </c>
+      <c r="X6">
+        <v>221.94</v>
+      </c>
+      <c r="Y6">
+        <v>233.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>115</v>
       </c>
@@ -12097,41 +12097,41 @@
       <c r="N7" s="2">
         <v>115</v>
       </c>
-      <c r="O7" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P7" s="2">
-        <v>40.369999999999997</v>
-      </c>
-      <c r="Q7" s="2">
-        <v>80.319999999999993</v>
-      </c>
-      <c r="R7" s="2">
-        <v>117.72</v>
-      </c>
-      <c r="S7" s="2">
-        <v>149.25</v>
-      </c>
-      <c r="T7" s="2">
-        <v>173.09</v>
-      </c>
-      <c r="U7" s="2">
-        <v>191.05</v>
-      </c>
-      <c r="V7" s="2">
-        <v>205.76</v>
-      </c>
-      <c r="W7" s="2">
-        <v>219.03</v>
-      </c>
-      <c r="X7" s="2">
-        <v>231.37</v>
-      </c>
-      <c r="Y7" s="2">
-        <v>242.78</v>
+      <c r="O7">
+        <v>-0.15</v>
+      </c>
+      <c r="P7">
+        <v>40.159999999999997</v>
+      </c>
+      <c r="Q7">
+        <v>79.930000000000007</v>
+      </c>
+      <c r="R7">
+        <v>114.23</v>
+      </c>
+      <c r="S7">
+        <v>140.4</v>
+      </c>
+      <c r="T7">
+        <v>160.30000000000001</v>
+      </c>
+      <c r="U7">
+        <v>176.97</v>
+      </c>
+      <c r="V7">
+        <v>191.51</v>
+      </c>
+      <c r="W7">
+        <v>204.73</v>
+      </c>
+      <c r="X7">
+        <v>216.9</v>
+      </c>
+      <c r="Y7">
+        <v>227.93</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>120</v>
       </c>
@@ -12171,41 +12171,41 @@
       <c r="N8" s="2">
         <v>120</v>
       </c>
-      <c r="O8" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P8" s="2">
-        <v>38.57</v>
-      </c>
-      <c r="Q8" s="2">
-        <v>76.78</v>
-      </c>
-      <c r="R8" s="2">
-        <v>112.74</v>
-      </c>
-      <c r="S8" s="2">
-        <v>144.36000000000001</v>
-      </c>
-      <c r="T8" s="2">
-        <v>168.73</v>
-      </c>
-      <c r="U8" s="2">
-        <v>187</v>
-      </c>
-      <c r="V8" s="2">
-        <v>201.67</v>
-      </c>
-      <c r="W8" s="2">
-        <v>214.83</v>
-      </c>
-      <c r="X8" s="2">
-        <v>227.1</v>
-      </c>
-      <c r="Y8" s="2">
-        <v>238.63</v>
+      <c r="O8">
+        <v>-0.13</v>
+      </c>
+      <c r="P8">
+        <v>38.229999999999997</v>
+      </c>
+      <c r="Q8">
+        <v>76.239999999999995</v>
+      </c>
+      <c r="R8">
+        <v>109.39</v>
+      </c>
+      <c r="S8">
+        <v>135.44</v>
+      </c>
+      <c r="T8">
+        <v>155.15</v>
+      </c>
+      <c r="U8">
+        <v>171.43</v>
+      </c>
+      <c r="V8">
+        <v>185.79</v>
+      </c>
+      <c r="W8">
+        <v>198.7</v>
+      </c>
+      <c r="X8">
+        <v>210.14</v>
+      </c>
+      <c r="Y8">
+        <v>220.05</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>125</v>
       </c>
@@ -12245,41 +12245,41 @@
       <c r="N9" s="2">
         <v>125</v>
       </c>
-      <c r="O9" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P9" s="2">
-        <v>36.47</v>
-      </c>
-      <c r="Q9" s="2">
-        <v>72.650000000000006</v>
-      </c>
-      <c r="R9" s="2">
-        <v>106.84</v>
-      </c>
-      <c r="S9" s="2">
-        <v>137.88</v>
-      </c>
-      <c r="T9" s="2">
-        <v>162.91999999999999</v>
-      </c>
-      <c r="U9" s="2">
-        <v>181.75</v>
-      </c>
-      <c r="V9" s="2">
-        <v>196.48</v>
-      </c>
-      <c r="W9" s="2">
-        <v>209.48</v>
-      </c>
-      <c r="X9" s="2">
-        <v>221.58</v>
-      </c>
-      <c r="Y9" s="2">
-        <v>233.01</v>
+      <c r="O9">
+        <v>-0.09</v>
+      </c>
+      <c r="P9">
+        <v>35.94</v>
+      </c>
+      <c r="Q9">
+        <v>71.62</v>
+      </c>
+      <c r="R9">
+        <v>103.36</v>
+      </c>
+      <c r="S9">
+        <v>129.19999999999999</v>
+      </c>
+      <c r="T9">
+        <v>148.81</v>
+      </c>
+      <c r="U9">
+        <v>164.79</v>
+      </c>
+      <c r="V9">
+        <v>178.63</v>
+      </c>
+      <c r="W9">
+        <v>190.7</v>
+      </c>
+      <c r="X9">
+        <v>200.99</v>
+      </c>
+      <c r="Y9">
+        <v>210.05</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>130</v>
       </c>
@@ -12319,41 +12319,41 @@
       <c r="N10" s="2">
         <v>130</v>
       </c>
-      <c r="O10" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P10" s="2">
-        <v>34.090000000000003</v>
-      </c>
-      <c r="Q10" s="2">
-        <v>67.97</v>
-      </c>
-      <c r="R10" s="2">
-        <v>100.09</v>
-      </c>
-      <c r="S10" s="2">
-        <v>129.84</v>
-      </c>
-      <c r="T10" s="2">
-        <v>155.26</v>
-      </c>
-      <c r="U10" s="2">
-        <v>174.95</v>
-      </c>
-      <c r="V10" s="2">
-        <v>189.94</v>
-      </c>
-      <c r="W10" s="2">
-        <v>202.85</v>
-      </c>
-      <c r="X10" s="2">
-        <v>214.69</v>
-      </c>
-      <c r="Y10" s="2">
-        <v>225.89</v>
+      <c r="O10">
+        <v>0.31</v>
+      </c>
+      <c r="P10">
+        <v>33.83</v>
+      </c>
+      <c r="Q10">
+        <v>66.790000000000006</v>
+      </c>
+      <c r="R10">
+        <v>96.74</v>
+      </c>
+      <c r="S10">
+        <v>121.92</v>
+      </c>
+      <c r="T10">
+        <v>141.1</v>
+      </c>
+      <c r="U10">
+        <v>156.69999999999999</v>
+      </c>
+      <c r="V10">
+        <v>169.71</v>
+      </c>
+      <c r="W10">
+        <v>180.59</v>
+      </c>
+      <c r="X10">
+        <v>189.99</v>
+      </c>
+      <c r="Y10">
+        <v>198.37</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>135</v>
       </c>
@@ -12393,41 +12393,41 @@
       <c r="N11" s="2">
         <v>135</v>
       </c>
-      <c r="O11" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P11" s="2">
-        <v>31.45</v>
-      </c>
-      <c r="Q11" s="2">
-        <v>62.77</v>
-      </c>
-      <c r="R11" s="2">
-        <v>92.56</v>
-      </c>
-      <c r="S11" s="2">
-        <v>120.46</v>
-      </c>
-      <c r="T11" s="2">
-        <v>145.41999999999999</v>
-      </c>
-      <c r="U11" s="2">
-        <v>165.89</v>
-      </c>
-      <c r="V11" s="2">
-        <v>181.52</v>
-      </c>
-      <c r="W11" s="2">
-        <v>194.54</v>
-      </c>
-      <c r="X11" s="2">
-        <v>206.22</v>
-      </c>
-      <c r="Y11" s="2">
-        <v>217.1</v>
+      <c r="O11">
+        <v>0.9</v>
+      </c>
+      <c r="P11">
+        <v>31.85</v>
+      </c>
+      <c r="Q11">
+        <v>61.99</v>
+      </c>
+      <c r="R11">
+        <v>89.83</v>
+      </c>
+      <c r="S11">
+        <v>113.8</v>
+      </c>
+      <c r="T11">
+        <v>132.18</v>
+      </c>
+      <c r="U11">
+        <v>146.91</v>
+      </c>
+      <c r="V11">
+        <v>158.74</v>
+      </c>
+      <c r="W11">
+        <v>168.67</v>
+      </c>
+      <c r="X11">
+        <v>177.31</v>
+      </c>
+      <c r="Y11">
+        <v>185.13</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>140</v>
       </c>
@@ -12467,41 +12467,41 @@
       <c r="N12" s="2">
         <v>140</v>
       </c>
-      <c r="O12" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P12" s="2">
-        <v>28.57</v>
-      </c>
-      <c r="Q12" s="2">
-        <v>57.08</v>
-      </c>
-      <c r="R12" s="2">
-        <v>84.29</v>
-      </c>
-      <c r="S12" s="2">
-        <v>109.94</v>
-      </c>
-      <c r="T12" s="2">
-        <v>133.63999999999999</v>
-      </c>
-      <c r="U12" s="2">
-        <v>154.05000000000001</v>
-      </c>
-      <c r="V12" s="2">
-        <v>170.3</v>
-      </c>
-      <c r="W12" s="2">
-        <v>183.74</v>
-      </c>
-      <c r="X12" s="2">
-        <v>195.52</v>
-      </c>
-      <c r="Y12" s="2">
-        <v>206.28</v>
+      <c r="O12">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="P12">
+        <v>29.55</v>
+      </c>
+      <c r="Q12">
+        <v>56.86</v>
+      </c>
+      <c r="R12">
+        <v>82.37</v>
+      </c>
+      <c r="S12">
+        <v>104.63</v>
+      </c>
+      <c r="T12">
+        <v>122.05</v>
+      </c>
+      <c r="U12">
+        <v>135.58000000000001</v>
+      </c>
+      <c r="V12">
+        <v>146.24</v>
+      </c>
+      <c r="W12">
+        <v>155.27000000000001</v>
+      </c>
+      <c r="X12">
+        <v>163.22</v>
+      </c>
+      <c r="Y12">
+        <v>170.43</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>145</v>
       </c>
@@ -12541,41 +12541,41 @@
       <c r="N13" s="2">
         <v>145</v>
       </c>
-      <c r="O13" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P13" s="2">
-        <v>25.47</v>
-      </c>
-      <c r="Q13" s="2">
-        <v>50.95</v>
-      </c>
-      <c r="R13" s="2">
-        <v>75.34</v>
-      </c>
-      <c r="S13" s="2">
-        <v>98.42</v>
-      </c>
-      <c r="T13" s="2">
-        <v>120.19</v>
-      </c>
-      <c r="U13" s="2">
-        <v>139.88</v>
-      </c>
-      <c r="V13" s="2">
-        <v>156.22999999999999</v>
-      </c>
-      <c r="W13" s="2">
-        <v>169.45</v>
-      </c>
-      <c r="X13" s="2">
-        <v>181.15</v>
-      </c>
-      <c r="Y13" s="2">
-        <v>191.94</v>
+      <c r="O13">
+        <v>0.72</v>
+      </c>
+      <c r="P13">
+        <v>26.29</v>
+      </c>
+      <c r="Q13">
+        <v>50.66</v>
+      </c>
+      <c r="R13">
+        <v>73.64</v>
+      </c>
+      <c r="S13">
+        <v>94.05</v>
+      </c>
+      <c r="T13">
+        <v>110.54</v>
+      </c>
+      <c r="U13">
+        <v>122.9</v>
+      </c>
+      <c r="V13">
+        <v>132.52000000000001</v>
+      </c>
+      <c r="W13">
+        <v>140.61000000000001</v>
+      </c>
+      <c r="X13">
+        <v>147.63999999999999</v>
+      </c>
+      <c r="Y13">
+        <v>154.07</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>150</v>
       </c>
@@ -12615,41 +12615,41 @@
       <c r="N14" s="2">
         <v>150</v>
       </c>
-      <c r="O14" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P14" s="2">
-        <v>22.19</v>
-      </c>
-      <c r="Q14" s="2">
-        <v>44.42</v>
-      </c>
-      <c r="R14" s="2">
-        <v>65.78</v>
-      </c>
-      <c r="S14" s="2">
-        <v>86.04</v>
-      </c>
-      <c r="T14" s="2">
-        <v>105.36</v>
-      </c>
-      <c r="U14" s="2">
-        <v>123.45</v>
-      </c>
-      <c r="V14" s="2">
-        <v>139.56</v>
-      </c>
-      <c r="W14" s="2">
-        <v>152.61000000000001</v>
-      </c>
-      <c r="X14" s="2">
-        <v>163.58000000000001</v>
-      </c>
-      <c r="Y14" s="2">
-        <v>173.47</v>
+      <c r="O14">
+        <v>-0.22</v>
+      </c>
+      <c r="P14">
+        <v>22.13</v>
+      </c>
+      <c r="Q14">
+        <v>43.47</v>
+      </c>
+      <c r="R14">
+        <v>63.84</v>
+      </c>
+      <c r="S14">
+        <v>82.25</v>
+      </c>
+      <c r="T14">
+        <v>97.51</v>
+      </c>
+      <c r="U14">
+        <v>108.65</v>
+      </c>
+      <c r="V14">
+        <v>117.17</v>
+      </c>
+      <c r="W14">
+        <v>124.27</v>
+      </c>
+      <c r="X14">
+        <v>130.41999999999999</v>
+      </c>
+      <c r="Y14">
+        <v>136.22</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>155</v>
       </c>
@@ -12689,41 +12689,41 @@
       <c r="N15" s="2">
         <v>155</v>
       </c>
-      <c r="O15" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P15" s="2">
-        <v>18.739999999999998</v>
-      </c>
-      <c r="Q15" s="2">
-        <v>37.54</v>
-      </c>
-      <c r="R15" s="2">
-        <v>55.67</v>
-      </c>
-      <c r="S15" s="2">
-        <v>72.91</v>
-      </c>
-      <c r="T15" s="2">
-        <v>89.42</v>
-      </c>
-      <c r="U15" s="2">
-        <v>105.19</v>
-      </c>
-      <c r="V15" s="2">
-        <v>119.94</v>
-      </c>
-      <c r="W15" s="2">
-        <v>133.03</v>
-      </c>
-      <c r="X15" s="2">
-        <v>143.80000000000001</v>
-      </c>
-      <c r="Y15" s="2">
-        <v>153</v>
+      <c r="O15">
+        <v>-1.1299999999999999</v>
+      </c>
+      <c r="P15">
+        <v>17.8</v>
+      </c>
+      <c r="Q15">
+        <v>35.979999999999997</v>
+      </c>
+      <c r="R15">
+        <v>53.53</v>
+      </c>
+      <c r="S15">
+        <v>69.680000000000007</v>
+      </c>
+      <c r="T15">
+        <v>83.45</v>
+      </c>
+      <c r="U15">
+        <v>93.26</v>
+      </c>
+      <c r="V15">
+        <v>100.46</v>
+      </c>
+      <c r="W15">
+        <v>106.42</v>
+      </c>
+      <c r="X15">
+        <v>111.69</v>
+      </c>
+      <c r="Y15">
+        <v>116.61</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>160</v>
       </c>
@@ -12763,41 +12763,41 @@
       <c r="N16" s="2">
         <v>160</v>
       </c>
-      <c r="O16" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P16" s="2">
-        <v>15.16</v>
-      </c>
-      <c r="Q16" s="2">
-        <v>30.37</v>
-      </c>
-      <c r="R16" s="2">
-        <v>45.11</v>
-      </c>
-      <c r="S16" s="2">
-        <v>59.15</v>
-      </c>
-      <c r="T16" s="2">
-        <v>72.599999999999994</v>
-      </c>
-      <c r="U16" s="2">
-        <v>85.66</v>
-      </c>
-      <c r="V16" s="2">
-        <v>98.24</v>
-      </c>
-      <c r="W16" s="2">
-        <v>110.04</v>
-      </c>
-      <c r="X16" s="2">
-        <v>120.54</v>
-      </c>
-      <c r="Y16" s="2">
-        <v>129.41</v>
+      <c r="O16">
+        <v>-1.51</v>
+      </c>
+      <c r="P16">
+        <v>13.87</v>
+      </c>
+      <c r="Q16">
+        <v>28.74</v>
+      </c>
+      <c r="R16">
+        <v>43.18</v>
+      </c>
+      <c r="S16">
+        <v>56.72</v>
+      </c>
+      <c r="T16">
+        <v>68.59</v>
+      </c>
+      <c r="U16">
+        <v>76.849999999999994</v>
+      </c>
+      <c r="V16">
+        <v>82.56</v>
+      </c>
+      <c r="W16">
+        <v>87.07</v>
+      </c>
+      <c r="X16">
+        <v>91.15</v>
+      </c>
+      <c r="Y16">
+        <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>165</v>
       </c>
@@ -12837,41 +12837,41 @@
       <c r="N17" s="2">
         <v>165</v>
       </c>
-      <c r="O17" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P17" s="2">
-        <v>11.46</v>
-      </c>
-      <c r="Q17" s="2">
-        <v>22.97</v>
-      </c>
-      <c r="R17" s="2">
-        <v>34.17</v>
-      </c>
-      <c r="S17" s="2">
-        <v>44.87</v>
-      </c>
-      <c r="T17" s="2">
-        <v>55.2</v>
-      </c>
-      <c r="U17" s="2">
-        <v>65.25</v>
-      </c>
-      <c r="V17" s="2">
-        <v>75.010000000000005</v>
-      </c>
-      <c r="W17" s="2">
-        <v>84.43</v>
-      </c>
-      <c r="X17" s="2">
-        <v>93.35</v>
-      </c>
-      <c r="Y17" s="2">
-        <v>101.42</v>
+      <c r="O17">
+        <v>-1.2</v>
+      </c>
+      <c r="P17">
+        <v>10.53</v>
+      </c>
+      <c r="Q17">
+        <v>21.93</v>
+      </c>
+      <c r="R17">
+        <v>33.06</v>
+      </c>
+      <c r="S17">
+        <v>43.6</v>
+      </c>
+      <c r="T17">
+        <v>53.07</v>
+      </c>
+      <c r="U17">
+        <v>59.09</v>
+      </c>
+      <c r="V17">
+        <v>62.86</v>
+      </c>
+      <c r="W17">
+        <v>66.12</v>
+      </c>
+      <c r="X17">
+        <v>69.099999999999994</v>
+      </c>
+      <c r="Y17">
+        <v>71.92</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>170</v>
       </c>
@@ -12911,41 +12911,41 @@
       <c r="N18" s="2">
         <v>170</v>
       </c>
-      <c r="O18" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P18" s="2">
-        <v>7.68</v>
-      </c>
-      <c r="Q18" s="2">
-        <v>15.39</v>
-      </c>
-      <c r="R18" s="2">
-        <v>22.95</v>
-      </c>
-      <c r="S18" s="2">
-        <v>30.19</v>
-      </c>
-      <c r="T18" s="2">
-        <v>37.31</v>
-      </c>
-      <c r="U18" s="2">
-        <v>44.15</v>
-      </c>
-      <c r="V18" s="2">
-        <v>50.78</v>
-      </c>
-      <c r="W18" s="2">
-        <v>57.21</v>
-      </c>
-      <c r="X18" s="2">
-        <v>63.44</v>
-      </c>
-      <c r="Y18" s="2">
-        <v>69.41</v>
+      <c r="O18">
+        <v>-0.56999999999999995</v>
+      </c>
+      <c r="P18">
+        <v>7.39</v>
+      </c>
+      <c r="Q18">
+        <v>15.18</v>
+      </c>
+      <c r="R18">
+        <v>22.8</v>
+      </c>
+      <c r="S18">
+        <v>30.01</v>
+      </c>
+      <c r="T18">
+        <v>36.25</v>
+      </c>
+      <c r="U18">
+        <v>39.75</v>
+      </c>
+      <c r="V18">
+        <v>42.11</v>
+      </c>
+      <c r="W18">
+        <v>44.19</v>
+      </c>
+      <c r="X18">
+        <v>46.28</v>
+      </c>
+      <c r="Y18">
+        <v>48.26</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>175</v>
       </c>
@@ -12985,41 +12985,41 @@
       <c r="N19" s="2">
         <v>175</v>
       </c>
-      <c r="O19" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="P19" s="2">
-        <v>3.85</v>
-      </c>
-      <c r="Q19" s="2">
-        <v>7.71</v>
-      </c>
-      <c r="R19" s="2">
-        <v>11.51</v>
-      </c>
-      <c r="S19" s="2">
-        <v>15.2</v>
-      </c>
-      <c r="T19" s="2">
-        <v>18.88</v>
-      </c>
-      <c r="U19" s="2">
-        <v>22.41</v>
-      </c>
-      <c r="V19" s="2">
-        <v>25.76</v>
-      </c>
-      <c r="W19" s="2">
-        <v>28.98</v>
-      </c>
-      <c r="X19" s="2">
-        <v>32.090000000000003</v>
-      </c>
-      <c r="Y19" s="2">
-        <v>35.119999999999997</v>
+      <c r="O19">
+        <v>-0.11</v>
+      </c>
+      <c r="P19">
+        <v>3.96</v>
+      </c>
+      <c r="Q19">
+        <v>7.92</v>
+      </c>
+      <c r="R19">
+        <v>11.69</v>
+      </c>
+      <c r="S19">
+        <v>15.15</v>
+      </c>
+      <c r="T19">
+        <v>18.32</v>
+      </c>
+      <c r="U19">
+        <v>19.91</v>
+      </c>
+      <c r="V19">
+        <v>20.97</v>
+      </c>
+      <c r="W19">
+        <v>22.18</v>
+      </c>
+      <c r="X19">
+        <v>23.27</v>
+      </c>
+      <c r="Y19">
+        <v>24.29</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>180</v>
       </c>
@@ -13059,41 +13059,41 @@
       <c r="N20" s="2">
         <v>180</v>
       </c>
-      <c r="O20" s="2">
+      <c r="O20">
         <v>-0.01</v>
       </c>
-      <c r="P20" s="2">
-        <v>-0.01</v>
-      </c>
-      <c r="Q20" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="R20" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="S20" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="T20" s="2">
-        <v>-0.02</v>
-      </c>
-      <c r="U20" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="V20" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="W20" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="X20" s="2">
-        <v>-0.03</v>
-      </c>
-      <c r="Y20" s="2">
-        <v>-0.03</v>
+      <c r="P20">
+        <v>0</v>
+      </c>
+      <c r="Q20">
+        <v>0.01</v>
+      </c>
+      <c r="R20">
+        <v>0.01</v>
+      </c>
+      <c r="S20">
+        <v>0.01</v>
+      </c>
+      <c r="T20">
+        <v>0.01</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0.01</v>
+      </c>
+      <c r="Y20">
+        <v>0.01</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -13128,7 +13128,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>90</v>
       </c>
@@ -13166,7 +13166,7 @@
         <v>263.44</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>95</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>261.91000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>100</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>260.39</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>105</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>258.88</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>110</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>255.29</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>115</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>250.66</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>120</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>246.07</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>125</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>239.41</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>130</v>
       </c>
@@ -13470,7 +13470,7 @@
         <v>232.33</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>135</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>220.15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>140</v>
       </c>
@@ -13546,7 +13546,7 @@
         <v>209.66</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>145</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v>196.58</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>150</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>180.04</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>155</v>
       </c>
@@ -13660,7 +13660,7 @@
         <v>159.79</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>160</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>135.16</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>165</v>
       </c>
@@ -13736,7 +13736,7 @@
         <v>106.69</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>170</v>
       </c>
@@ -13774,7 +13774,7 @@
         <v>74.83</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>175</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>41.68</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>180</v>
       </c>
@@ -13860,9 +13860,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1.6605200000000001E-2</v>
       </c>
@@ -13881,9 +13881,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -13921,7 +13921,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>90</v>
       </c>
@@ -13959,7 +13959,7 @@
         <v>226.44</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>95</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>247.67</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>100</v>
       </c>
@@ -14035,7 +14035,7 @@
         <v>268.89999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>105</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>289.66000000000003</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>110</v>
       </c>
@@ -14111,7 +14111,7 @@
         <v>308.77</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>115</v>
       </c>
@@ -14149,7 +14149,7 @@
         <v>325.42</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>120</v>
       </c>
@@ -14187,7 +14187,7 @@
         <v>338.95</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>125</v>
       </c>
@@ -14225,7 +14225,7 @@
         <v>348.7</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>130</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>354.22</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>135</v>
       </c>
@@ -14301,7 +14301,7 @@
         <v>355.03</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>140</v>
       </c>
@@ -14339,7 +14339,7 @@
         <v>349.92</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>145</v>
       </c>
@@ -14377,7 +14377,7 @@
         <v>335.92</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>150</v>
       </c>
@@ -14415,7 +14415,7 @@
         <v>310.44</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>155</v>
       </c>
@@ -14453,7 +14453,7 @@
         <v>276.62</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>160</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>234.92</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>165</v>
       </c>
@@ -14529,7 +14529,7 @@
         <v>184.97</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>170</v>
       </c>
@@ -14567,7 +14567,7 @@
         <v>126.54</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>175</v>
       </c>
@@ -14605,7 +14605,7 @@
         <v>63.83</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>180</v>
       </c>
@@ -14643,7 +14643,7 @@
         <v>-0.05</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -14681,7 +14681,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>90</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>95</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>100</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>105</v>
       </c>
@@ -14833,7 +14833,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>110</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>115</v>
       </c>
@@ -14909,7 +14909,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>120</v>
       </c>
@@ -14947,7 +14947,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>125</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>130</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>360.6</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>135</v>
       </c>
@@ -15061,7 +15061,7 @@
         <v>361.4</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>140</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>354.8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>145</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>340.1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>150</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>317.10000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>155</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>284.3</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>160</v>
       </c>
@@ -15251,7 +15251,7 @@
         <v>243.1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>165</v>
       </c>
@@ -15289,7 +15289,7 @@
         <v>192.4</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>170</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>133.4</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>175</v>
       </c>
@@ -15365,7 +15365,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.65">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>180</v>
       </c>

--- a/ref_file/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
+++ b/ref_file/FEMM_폴페어일렉트로닉스_dq_torque비교.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\1.업무폴더\2026년도업무\5.전략연구사업\IONIQ5_FEMM\ref_file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sjo\fem_temp\femm_ioniq5\ref_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12975"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12973" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Lambda_d_matrix" sheetId="1" r:id="rId1"/>
@@ -1408,11 +1408,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-32049312"/>
-        <c:axId val="-32059104"/>
+        <c:axId val="2137873248"/>
+        <c:axId val="2137873792"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-32049312"/>
+        <c:axId val="2137873248"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1455,7 +1455,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-32059104"/>
+        <c:crossAx val="2137873792"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1463,7 +1463,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-32059104"/>
+        <c:axId val="2137873792"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1514,7 +1514,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-32049312"/>
+        <c:crossAx val="2137873248"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2296,11 +2296,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-32058560"/>
-        <c:axId val="-32055840"/>
+        <c:axId val="2137871616"/>
+        <c:axId val="2137869440"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-32058560"/>
+        <c:axId val="2137871616"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2343,7 +2343,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-32055840"/>
+        <c:crossAx val="2137869440"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2351,7 +2351,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-32055840"/>
+        <c:axId val="2137869440"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2402,7 +2402,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-32058560"/>
+        <c:crossAx val="2137871616"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3002,37 +3002,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>-0.01</c:v>
+                  <c:v>-0.02</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>45.19</c:v>
+                  <c:v>-45.17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>89.22</c:v>
+                  <c:v>-89.21</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>127.04</c:v>
+                  <c:v>-127.04</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>154.22999999999999</c:v>
+                  <c:v>-154.22999999999999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>175.82</c:v>
+                  <c:v>-175.82</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>194.62</c:v>
+                  <c:v>-194.64</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>211.19</c:v>
+                  <c:v>-211.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>225.12</c:v>
+                  <c:v>-225.14</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>237.22</c:v>
+                  <c:v>-237.23</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>248.25</c:v>
+                  <c:v>-248.26</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3114,37 +3114,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>-0.11</c:v>
+                  <c:v>-0.1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.96</c:v>
+                  <c:v>-4.22</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.92</c:v>
+                  <c:v>-8.2799999999999994</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>11.69</c:v>
+                  <c:v>-12.08</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15.15</c:v>
+                  <c:v>-15.5</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>18.32</c:v>
+                  <c:v>-18.88</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>19.91</c:v>
+                  <c:v>-22.13</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>20.97</c:v>
+                  <c:v>-25.2</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>22.18</c:v>
+                  <c:v>-28.17</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>23.27</c:v>
+                  <c:v>-31.07</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>24.29</c:v>
+                  <c:v>-33.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3160,11 +3160,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-32055296"/>
-        <c:axId val="-32054752"/>
+        <c:axId val="2140301408"/>
+        <c:axId val="2140300864"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-32055296"/>
+        <c:axId val="2140301408"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3207,7 +3207,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-32054752"/>
+        <c:crossAx val="2140300864"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3215,7 +3215,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-32054752"/>
+        <c:axId val="2140300864"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3266,7 +3266,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-32055296"/>
+        <c:crossAx val="2140301408"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3786,61 +3786,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>248.25</c:v>
+                  <c:v>-248.26</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>245.16</c:v>
+                  <c:v>-250.25</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>241.5</c:v>
+                  <c:v>-250.63</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>237.62</c:v>
+                  <c:v>-249.17</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>233.4</c:v>
+                  <c:v>-246.4</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>227.93</c:v>
+                  <c:v>-242.72</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>220.05</c:v>
+                  <c:v>-238.53</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>210.05</c:v>
+                  <c:v>-233.72</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>198.37</c:v>
+                  <c:v>-228.09</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>185.13</c:v>
+                  <c:v>-221.36</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>170.43</c:v>
+                  <c:v>-212.91</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>154.07</c:v>
+                  <c:v>-200.63</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>136.22</c:v>
+                  <c:v>-181.59</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>116.61</c:v>
+                  <c:v>-157.16</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>95</c:v>
+                  <c:v>-129.93</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>71.92</c:v>
+                  <c:v>-100.39</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>48.26</c:v>
+                  <c:v>-68.27</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>24.29</c:v>
+                  <c:v>-33.9</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.01</c:v>
+                  <c:v>-0.03</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4266,61 +4266,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>45.19</c:v>
+                  <c:v>-45.17</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43.94</c:v>
+                  <c:v>-45.92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>42.79</c:v>
+                  <c:v>-45.52</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>42.02</c:v>
+                  <c:v>-44.08</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>41.33</c:v>
+                  <c:v>-42.21</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>40.159999999999997</c:v>
+                  <c:v>-40.43</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>38.229999999999997</c:v>
+                  <c:v>-38.64</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35.94</c:v>
+                  <c:v>-36.479999999999997</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>33.83</c:v>
+                  <c:v>-33.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>31.85</c:v>
+                  <c:v>-30.46</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>29.55</c:v>
+                  <c:v>-27.52</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>26.29</c:v>
+                  <c:v>-25.16</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>22.13</c:v>
+                  <c:v>-23</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>17.8</c:v>
+                  <c:v>-20.54</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>13.87</c:v>
+                  <c:v>-17.27</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>10.53</c:v>
+                  <c:v>-13.17</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>7.39</c:v>
+                  <c:v>-8.65</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>3.96</c:v>
+                  <c:v>-4.22</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0</c:v>
+                  <c:v>-0.01</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4336,11 +4336,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-256917184"/>
-        <c:axId val="-256919904"/>
+        <c:axId val="2140298688"/>
+        <c:axId val="2140303584"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-256917184"/>
+        <c:axId val="2140298688"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4383,7 +4383,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-256919904"/>
+        <c:crossAx val="2140303584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4391,7 +4391,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-256919904"/>
+        <c:axId val="2140303584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4442,7 +4442,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-256917184"/>
+        <c:crossAx val="2140298688"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4596,61 +4596,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>226.44</c:v>
+                  <c:v>-233.32</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>247.67</c:v>
+                  <c:v>-264.51</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>268.89999999999998</c:v>
+                  <c:v>-293.11</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>289.66000000000003</c:v>
+                  <c:v>-311.49</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>308.77</c:v>
+                  <c:v>-319.97000000000003</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>325.42</c:v>
+                  <c:v>-326.51</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>338.95</c:v>
+                  <c:v>-338.14</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>348.7</c:v>
+                  <c:v>-354.75</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>354.22</c:v>
+                  <c:v>-367.54</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>355.03</c:v>
+                  <c:v>-369.88</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>349.92</c:v>
+                  <c:v>-357.55</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>335.92</c:v>
+                  <c:v>-331.09</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>310.44</c:v>
+                  <c:v>-298.55</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>276.62</c:v>
+                  <c:v>-261.26</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>234.92</c:v>
+                  <c:v>-223.81</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>184.97</c:v>
+                  <c:v>-185.61</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>126.54</c:v>
+                  <c:v>-134.16</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>63.83</c:v>
+                  <c:v>-67.19</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>-0.05</c:v>
+                  <c:v>-7.0000000000000007E-2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4878,58 +4878,58 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>27.56</c:v>
+                  <c:v>-25.54</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>28</c:v>
+                  <c:v>-28.17</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>28.21</c:v>
+                  <c:v>-30.01</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>28.18</c:v>
+                  <c:v>-29.61</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>27.91</c:v>
+                  <c:v>-27.6</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27.37</c:v>
+                  <c:v>-26.08</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>26.58</c:v>
+                  <c:v>-26.56</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>25.52</c:v>
+                  <c:v>-27.73</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>24.2</c:v>
+                  <c:v>-27.2</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>22.62</c:v>
+                  <c:v>-23.92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>20.8</c:v>
+                  <c:v>-19.68</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>18.75</c:v>
+                  <c:v>-16.57</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>16.489999999999998</c:v>
+                  <c:v>-15.25</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>14.05</c:v>
+                  <c:v>-14.25</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11.44</c:v>
+                  <c:v>-12.17</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8.6999999999999993</c:v>
+                  <c:v>-8.3699999999999992</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>5.85</c:v>
+                  <c:v>-3.95</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>2.94</c:v>
+                  <c:v>-0.99</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>0</c:v>
@@ -4948,11 +4948,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-256927520"/>
-        <c:axId val="-286198032"/>
+        <c:axId val="2140301952"/>
+        <c:axId val="2140303040"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-256927520"/>
+        <c:axId val="2140301952"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4994,7 +4994,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-286198032"/>
+        <c:crossAx val="2140303040"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5002,7 +5002,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-286198032"/>
+        <c:axId val="2140303040"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5053,7 +5053,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-256927520"/>
+        <c:crossAx val="2140301952"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5158,34 +5158,34 @@
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>27.56</c:v>
+                  <c:v>-25.54</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>54.87</c:v>
+                  <c:v>-50.96</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>81.72</c:v>
+                  <c:v>-76.709999999999994</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>107.87</c:v>
+                  <c:v>-101.98</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>133.41</c:v>
+                  <c:v>-127.06</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>156.19999999999999</c:v>
+                  <c:v>-152.18</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>175.43</c:v>
+                  <c:v>-176.19</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>193.07</c:v>
+                  <c:v>-197.09</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>209.92</c:v>
+                  <c:v>-215.72</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>226.44</c:v>
+                  <c:v>-233.32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5295,37 +5295,37 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="11"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>-0.2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>22.62</c:v>
+                  <c:v>-23.92</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>51.18</c:v>
+                  <c:v>-53.25</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>84.7</c:v>
+                  <c:v>-87.76</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>122.68</c:v>
+                  <c:v>-127.29</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>164.19</c:v>
+                  <c:v>-170.11</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>206.21</c:v>
+                  <c:v>-212.97</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>244.31</c:v>
+                  <c:v>-254.93</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>280.93</c:v>
+                  <c:v>-296.05</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>317.64999999999998</c:v>
+                  <c:v>-333.92</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>355.03</c:v>
+                  <c:v>-369.88</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5411,11 +5411,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-17300144"/>
-        <c:axId val="-17301232"/>
+        <c:axId val="2140299232"/>
+        <c:axId val="2140304672"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-17300144"/>
+        <c:axId val="2140299232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5457,7 +5457,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-17301232"/>
+        <c:crossAx val="2140304672"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5465,7 +5465,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-17301232"/>
+        <c:axId val="2140304672"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5516,7 +5516,7 @@
             <a:endParaRPr lang="ko-KR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-17300144"/>
+        <c:crossAx val="2140299232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9362,9 +9362,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -9438,7 +9438,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A2">
         <v>90</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>114.9</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A3">
         <v>95</v>
       </c>
@@ -9586,7 +9586,7 @@
         <v>103.84</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A4">
         <v>100</v>
       </c>
@@ -9660,7 +9660,7 @@
         <v>93.31</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A5">
         <v>105</v>
       </c>
@@ -9734,7 +9734,7 @@
         <v>83.68</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A6">
         <v>110</v>
       </c>
@@ -9808,7 +9808,7 @@
         <v>74.709999999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A7">
         <v>115</v>
       </c>
@@ -9882,7 +9882,7 @@
         <v>65.959999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A8">
         <v>120</v>
       </c>
@@ -9956,7 +9956,7 @@
         <v>57.22</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A9">
         <v>125</v>
       </c>
@@ -10030,7 +10030,7 @@
         <v>48.64</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A10">
         <v>130</v>
       </c>
@@ -10104,7 +10104,7 @@
         <v>40.340000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A11">
         <v>135</v>
       </c>
@@ -10178,7 +10178,7 @@
         <v>32.32</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A12">
         <v>140</v>
       </c>
@@ -10252,7 +10252,7 @@
         <v>24.07</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A13">
         <v>145</v>
       </c>
@@ -10326,7 +10326,7 @@
         <v>14.83</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A14">
         <v>150</v>
       </c>
@@ -10400,7 +10400,7 @@
         <v>4.91</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A15">
         <v>155</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>-4.51</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A16">
         <v>160</v>
       </c>
@@ -10548,7 +10548,7 @@
         <v>-12.93</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A17">
         <v>165</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>-19.61</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A18">
         <v>170</v>
       </c>
@@ -10696,7 +10696,7 @@
         <v>-23.99</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A19">
         <v>175</v>
       </c>
@@ -10770,7 +10770,7 @@
         <v>-26.22</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A20">
         <v>180</v>
       </c>
@@ -10844,7 +10844,7 @@
         <v>-26.92</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>2</v>
       </c>
@@ -10879,7 +10879,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A23">
         <v>90</v>
       </c>
@@ -10917,7 +10917,7 @@
         <v>122.91</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A24">
         <v>95</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>113.96</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A25">
         <v>100</v>
       </c>
@@ -10993,7 +10993,7 @@
         <v>105.1</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A26">
         <v>105</v>
       </c>
@@ -11031,7 +11031,7 @@
         <v>95.79</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A27">
         <v>110</v>
       </c>
@@ -11069,7 +11069,7 @@
         <v>86.04</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A28">
         <v>115</v>
       </c>
@@ -11107,7 +11107,7 @@
         <v>76.37</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A29">
         <v>120</v>
       </c>
@@ -11145,7 +11145,7 @@
         <v>66.78</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A30">
         <v>125</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>57.8</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A31">
         <v>130</v>
       </c>
@@ -11221,7 +11221,7 @@
         <v>47.53</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A32">
         <v>135</v>
       </c>
@@ -11259,7 +11259,7 @@
         <v>37.119999999999997</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A33">
         <v>140</v>
       </c>
@@ -11297,7 +11297,7 @@
         <v>27.75</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A34">
         <v>145</v>
       </c>
@@ -11335,7 +11335,7 @@
         <v>18.66</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A35">
         <v>150</v>
       </c>
@@ -11373,7 +11373,7 @@
         <v>9.19</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A36">
         <v>155</v>
       </c>
@@ -11411,7 +11411,7 @@
         <v>0.51</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A37">
         <v>160</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>-7.37</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A38">
         <v>165</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>-14.14</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A39">
         <v>170</v>
       </c>
@@ -11525,7 +11525,7 @@
         <v>-19.260000000000002</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A40">
         <v>175</v>
       </c>
@@ -11563,7 +11563,7 @@
         <v>-22.67</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A41">
         <v>180</v>
       </c>
@@ -11611,9 +11611,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Y41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -11687,7 +11687,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A2">
         <v>90</v>
       </c>
@@ -11728,40 +11728,40 @@
         <v>90</v>
       </c>
       <c r="O2">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="P2">
-        <v>45.19</v>
+        <v>-45.17</v>
       </c>
       <c r="Q2">
-        <v>89.22</v>
+        <v>-89.21</v>
       </c>
       <c r="R2">
-        <v>127.04</v>
+        <v>-127.04</v>
       </c>
       <c r="S2">
-        <v>154.22999999999999</v>
+        <v>-154.22999999999999</v>
       </c>
       <c r="T2">
-        <v>175.82</v>
+        <v>-175.82</v>
       </c>
       <c r="U2">
-        <v>194.62</v>
+        <v>-194.64</v>
       </c>
       <c r="V2">
-        <v>211.19</v>
+        <v>-211.2</v>
       </c>
       <c r="W2">
-        <v>225.12</v>
+        <v>-225.14</v>
       </c>
       <c r="X2">
-        <v>237.22</v>
+        <v>-237.23</v>
       </c>
       <c r="Y2">
-        <v>248.25</v>
+        <v>-248.26</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A3">
         <v>95</v>
       </c>
@@ -11802,40 +11802,40 @@
         <v>95</v>
       </c>
       <c r="O3">
-        <v>-0.95</v>
+        <v>-0.94</v>
       </c>
       <c r="P3">
-        <v>43.94</v>
+        <v>-45.92</v>
       </c>
       <c r="Q3">
-        <v>88.02</v>
+        <v>-89.66</v>
       </c>
       <c r="R3">
-        <v>125.78</v>
+        <v>-127.43</v>
       </c>
       <c r="S3">
-        <v>152.97</v>
+        <v>-154.71</v>
       </c>
       <c r="T3">
-        <v>174.86</v>
+        <v>-176.03</v>
       </c>
       <c r="U3">
-        <v>193.53</v>
+        <v>-194.6</v>
       </c>
       <c r="V3">
-        <v>209.09</v>
+        <v>-211.37</v>
       </c>
       <c r="W3">
-        <v>222.28</v>
+        <v>-226.31</v>
       </c>
       <c r="X3">
-        <v>234.13</v>
+        <v>-239.03</v>
       </c>
       <c r="Y3">
-        <v>245.16</v>
+        <v>-250.25</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A4">
         <v>100</v>
       </c>
@@ -11876,40 +11876,40 @@
         <v>100</v>
       </c>
       <c r="O4">
-        <v>-1.35</v>
+        <v>-1.37</v>
       </c>
       <c r="P4">
-        <v>42.79</v>
+        <v>-45.52</v>
       </c>
       <c r="Q4">
-        <v>86.49</v>
+        <v>-88.72</v>
       </c>
       <c r="R4">
-        <v>123.83</v>
+        <v>-126.75</v>
       </c>
       <c r="S4">
-        <v>151.05000000000001</v>
+        <v>-154.62</v>
       </c>
       <c r="T4">
-        <v>172.9</v>
+        <v>-175.63</v>
       </c>
       <c r="U4">
-        <v>190.71</v>
+        <v>-193.81</v>
       </c>
       <c r="V4">
-        <v>205.5</v>
+        <v>-210.35</v>
       </c>
       <c r="W4">
-        <v>218.45</v>
+        <v>-225.43</v>
       </c>
       <c r="X4">
-        <v>230.34</v>
+        <v>-238.87</v>
       </c>
       <c r="Y4">
-        <v>241.5</v>
+        <v>-250.63</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A5">
         <v>105</v>
       </c>
@@ -11950,40 +11950,40 @@
         <v>105</v>
       </c>
       <c r="O5">
-        <v>-1.0900000000000001</v>
+        <v>-1.1000000000000001</v>
       </c>
       <c r="P5">
-        <v>42.02</v>
+        <v>-44.08</v>
       </c>
       <c r="Q5">
-        <v>84.69</v>
+        <v>-86.54</v>
       </c>
       <c r="R5">
-        <v>121.28</v>
+        <v>-124.72</v>
       </c>
       <c r="S5">
-        <v>148.35</v>
+        <v>-154.1</v>
       </c>
       <c r="T5">
-        <v>169.51</v>
+        <v>-175</v>
       </c>
       <c r="U5">
-        <v>186.62</v>
+        <v>-192.6</v>
       </c>
       <c r="V5">
-        <v>201.12</v>
+        <v>-208.61</v>
       </c>
       <c r="W5">
-        <v>214.17</v>
+        <v>-223.43</v>
       </c>
       <c r="X5">
-        <v>226.26</v>
+        <v>-236.99</v>
       </c>
       <c r="Y5">
-        <v>237.62</v>
+        <v>-249.17</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A6">
         <v>110</v>
       </c>
@@ -12027,37 +12027,37 @@
         <v>-0.53</v>
       </c>
       <c r="P6">
-        <v>41.33</v>
+        <v>-42.21</v>
       </c>
       <c r="Q6">
-        <v>82.59</v>
+        <v>-83.58</v>
       </c>
       <c r="R6">
-        <v>118.16</v>
+        <v>-121.49</v>
       </c>
       <c r="S6">
-        <v>144.78</v>
+        <v>-152.69</v>
       </c>
       <c r="T6">
-        <v>165.15</v>
+        <v>-174.04</v>
       </c>
       <c r="U6">
-        <v>181.95</v>
+        <v>-191.17</v>
       </c>
       <c r="V6">
-        <v>196.47</v>
+        <v>-206.53</v>
       </c>
       <c r="W6">
-        <v>209.66</v>
+        <v>-220.83</v>
       </c>
       <c r="X6">
-        <v>221.94</v>
+        <v>-234.15</v>
       </c>
       <c r="Y6">
-        <v>233.4</v>
+        <v>-246.4</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A7">
         <v>115</v>
       </c>
@@ -12101,37 +12101,37 @@
         <v>-0.15</v>
       </c>
       <c r="P7">
-        <v>40.159999999999997</v>
+        <v>-40.43</v>
       </c>
       <c r="Q7">
-        <v>79.930000000000007</v>
+        <v>-80.319999999999993</v>
       </c>
       <c r="R7">
-        <v>114.23</v>
+        <v>-117.5</v>
       </c>
       <c r="S7">
-        <v>140.4</v>
+        <v>-149.30000000000001</v>
       </c>
       <c r="T7">
-        <v>160.30000000000001</v>
+        <v>-172.29</v>
       </c>
       <c r="U7">
-        <v>176.97</v>
+        <v>-189.4</v>
       </c>
       <c r="V7">
-        <v>191.51</v>
+        <v>-204.24</v>
       </c>
       <c r="W7">
-        <v>204.73</v>
+        <v>-217.92</v>
       </c>
       <c r="X7">
-        <v>216.9</v>
+        <v>-230.76</v>
       </c>
       <c r="Y7">
-        <v>227.93</v>
+        <v>-242.72</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A8">
         <v>120</v>
       </c>
@@ -12172,40 +12172,40 @@
         <v>120</v>
       </c>
       <c r="O8">
-        <v>-0.13</v>
+        <v>-0.12</v>
       </c>
       <c r="P8">
-        <v>38.229999999999997</v>
+        <v>-38.64</v>
       </c>
       <c r="Q8">
-        <v>76.239999999999995</v>
+        <v>-76.790000000000006</v>
       </c>
       <c r="R8">
-        <v>109.39</v>
+        <v>-112.69</v>
       </c>
       <c r="S8">
-        <v>135.44</v>
+        <v>-144.27000000000001</v>
       </c>
       <c r="T8">
-        <v>155.15</v>
+        <v>-168.62</v>
       </c>
       <c r="U8">
-        <v>171.43</v>
+        <v>-186.92</v>
       </c>
       <c r="V8">
-        <v>185.79</v>
+        <v>-201.6</v>
       </c>
       <c r="W8">
-        <v>198.7</v>
+        <v>-214.75</v>
       </c>
       <c r="X8">
-        <v>210.14</v>
+        <v>-227.02</v>
       </c>
       <c r="Y8">
-        <v>220.05</v>
+        <v>-238.53</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A9">
         <v>125</v>
       </c>
@@ -12246,40 +12246,40 @@
         <v>125</v>
       </c>
       <c r="O9">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="P9">
-        <v>35.94</v>
+        <v>-36.479999999999997</v>
       </c>
       <c r="Q9">
-        <v>71.62</v>
+        <v>-72.510000000000005</v>
       </c>
       <c r="R9">
-        <v>103.36</v>
+        <v>-106.81</v>
       </c>
       <c r="S9">
-        <v>129.19999999999999</v>
+        <v>-137.85</v>
       </c>
       <c r="T9">
-        <v>148.81</v>
+        <v>-162.61000000000001</v>
       </c>
       <c r="U9">
-        <v>164.79</v>
+        <v>-182.45</v>
       </c>
       <c r="V9">
-        <v>178.63</v>
+        <v>-198.08</v>
       </c>
       <c r="W9">
-        <v>190.7</v>
+        <v>-211.03</v>
       </c>
       <c r="X9">
-        <v>200.99</v>
+        <v>-222.76</v>
       </c>
       <c r="Y9">
-        <v>210.05</v>
+        <v>-233.72</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A10">
         <v>130</v>
       </c>
@@ -12320,40 +12320,40 @@
         <v>130</v>
       </c>
       <c r="O10">
-        <v>0.31</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="P10">
-        <v>33.83</v>
+        <v>-33.700000000000003</v>
       </c>
       <c r="Q10">
-        <v>66.790000000000006</v>
+        <v>-67.44</v>
       </c>
       <c r="R10">
-        <v>96.74</v>
+        <v>-99.7</v>
       </c>
       <c r="S10">
-        <v>121.92</v>
+        <v>-129.82</v>
       </c>
       <c r="T10">
-        <v>141.1</v>
+        <v>-155.35</v>
       </c>
       <c r="U10">
-        <v>156.69999999999999</v>
+        <v>-175.56</v>
       </c>
       <c r="V10">
-        <v>169.71</v>
+        <v>-192.6</v>
       </c>
       <c r="W10">
-        <v>180.59</v>
+        <v>-206.23</v>
       </c>
       <c r="X10">
-        <v>189.99</v>
+        <v>-217.68</v>
       </c>
       <c r="Y10">
-        <v>198.37</v>
+        <v>-228.09</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A11">
         <v>135</v>
       </c>
@@ -12394,40 +12394,40 @@
         <v>135</v>
       </c>
       <c r="O11">
-        <v>0.9</v>
+        <v>0.89</v>
       </c>
       <c r="P11">
-        <v>31.85</v>
+        <v>-30.46</v>
       </c>
       <c r="Q11">
-        <v>61.99</v>
+        <v>-61.91</v>
       </c>
       <c r="R11">
-        <v>89.83</v>
+        <v>-91.93</v>
       </c>
       <c r="S11">
-        <v>113.8</v>
+        <v>-120.36</v>
       </c>
       <c r="T11">
-        <v>132.18</v>
+        <v>-146.13999999999999</v>
       </c>
       <c r="U11">
-        <v>146.91</v>
+        <v>-167.11</v>
       </c>
       <c r="V11">
-        <v>158.74</v>
+        <v>-184.45</v>
       </c>
       <c r="W11">
-        <v>168.67</v>
+        <v>-199.31</v>
       </c>
       <c r="X11">
-        <v>177.31</v>
+        <v>-211.24</v>
       </c>
       <c r="Y11">
-        <v>185.13</v>
+        <v>-221.36</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A12">
         <v>140</v>
       </c>
@@ -12468,40 +12468,40 @@
         <v>140</v>
       </c>
       <c r="O12">
-        <v>1.1499999999999999</v>
+        <v>1.1399999999999999</v>
       </c>
       <c r="P12">
-        <v>29.55</v>
+        <v>-27.52</v>
       </c>
       <c r="Q12">
-        <v>56.86</v>
+        <v>-56.41</v>
       </c>
       <c r="R12">
-        <v>82.37</v>
+        <v>-84.07</v>
       </c>
       <c r="S12">
-        <v>104.63</v>
+        <v>-110.38</v>
       </c>
       <c r="T12">
-        <v>122.05</v>
+        <v>-135.02000000000001</v>
       </c>
       <c r="U12">
-        <v>135.58000000000001</v>
+        <v>-156.12</v>
       </c>
       <c r="V12">
-        <v>146.24</v>
+        <v>-173.96</v>
       </c>
       <c r="W12">
-        <v>155.27000000000001</v>
+        <v>-189.25</v>
       </c>
       <c r="X12">
-        <v>163.22</v>
+        <v>-202.35</v>
       </c>
       <c r="Y12">
-        <v>170.43</v>
+        <v>-212.91</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A13">
         <v>145</v>
       </c>
@@ -12545,37 +12545,37 @@
         <v>0.72</v>
       </c>
       <c r="P13">
-        <v>26.29</v>
+        <v>-25.16</v>
       </c>
       <c r="Q13">
-        <v>50.66</v>
+        <v>-51.18</v>
       </c>
       <c r="R13">
-        <v>73.64</v>
+        <v>-76.349999999999994</v>
       </c>
       <c r="S13">
-        <v>94.05</v>
+        <v>-100.28</v>
       </c>
       <c r="T13">
-        <v>110.54</v>
+        <v>-122.89</v>
       </c>
       <c r="U13">
-        <v>122.9</v>
+        <v>-142.66999999999999</v>
       </c>
       <c r="V13">
-        <v>132.52000000000001</v>
+        <v>-159.72</v>
       </c>
       <c r="W13">
-        <v>140.61000000000001</v>
+        <v>-175.12</v>
       </c>
       <c r="X13">
-        <v>147.63999999999999</v>
+        <v>-188.82</v>
       </c>
       <c r="Y13">
-        <v>154.07</v>
+        <v>-200.63</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A14">
         <v>150</v>
       </c>
@@ -12619,37 +12619,37 @@
         <v>-0.22</v>
       </c>
       <c r="P14">
-        <v>22.13</v>
+        <v>-23</v>
       </c>
       <c r="Q14">
-        <v>43.47</v>
+        <v>-45.96</v>
       </c>
       <c r="R14">
-        <v>63.84</v>
+        <v>-68.31</v>
       </c>
       <c r="S14">
-        <v>82.25</v>
+        <v>-89.5</v>
       </c>
       <c r="T14">
-        <v>97.51</v>
+        <v>-109.54</v>
       </c>
       <c r="U14">
-        <v>108.65</v>
+        <v>-127.31</v>
       </c>
       <c r="V14">
-        <v>117.17</v>
+        <v>-142.66</v>
       </c>
       <c r="W14">
-        <v>124.27</v>
+        <v>-156.61000000000001</v>
       </c>
       <c r="X14">
-        <v>130.41999999999999</v>
+        <v>-169.57</v>
       </c>
       <c r="Y14">
-        <v>136.22</v>
+        <v>-181.59</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A15">
         <v>155</v>
       </c>
@@ -12693,37 +12693,37 @@
         <v>-1.1299999999999999</v>
       </c>
       <c r="P15">
-        <v>17.8</v>
+        <v>-20.54</v>
       </c>
       <c r="Q15">
-        <v>35.979999999999997</v>
+        <v>-40.130000000000003</v>
       </c>
       <c r="R15">
-        <v>53.53</v>
+        <v>-59.21</v>
       </c>
       <c r="S15">
-        <v>69.680000000000007</v>
+        <v>-77.33</v>
       </c>
       <c r="T15">
-        <v>83.45</v>
+        <v>-94.47</v>
       </c>
       <c r="U15">
-        <v>93.26</v>
+        <v>-110.01</v>
       </c>
       <c r="V15">
-        <v>100.46</v>
+        <v>-123.36</v>
       </c>
       <c r="W15">
-        <v>106.42</v>
+        <v>-135.41999999999999</v>
       </c>
       <c r="X15">
-        <v>111.69</v>
+        <v>-146.63</v>
       </c>
       <c r="Y15">
-        <v>116.61</v>
+        <v>-157.16</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A16">
         <v>160</v>
       </c>
@@ -12764,40 +12764,40 @@
         <v>160</v>
       </c>
       <c r="O16">
-        <v>-1.51</v>
+        <v>-1.5</v>
       </c>
       <c r="P16">
-        <v>13.87</v>
+        <v>-17.27</v>
       </c>
       <c r="Q16">
-        <v>28.74</v>
+        <v>-33.21</v>
       </c>
       <c r="R16">
-        <v>43.18</v>
+        <v>-48.7</v>
       </c>
       <c r="S16">
-        <v>56.72</v>
+        <v>-63.33</v>
       </c>
       <c r="T16">
-        <v>68.59</v>
+        <v>-77.23</v>
       </c>
       <c r="U16">
-        <v>76.849999999999994</v>
+        <v>-90.21</v>
       </c>
       <c r="V16">
-        <v>82.56</v>
+        <v>-101.81</v>
       </c>
       <c r="W16">
-        <v>87.07</v>
+        <v>-111.94</v>
       </c>
       <c r="X16">
-        <v>91.15</v>
+        <v>-121.26</v>
       </c>
       <c r="Y16">
-        <v>95</v>
+        <v>-129.93</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A17">
         <v>165</v>
       </c>
@@ -12841,37 +12841,37 @@
         <v>-1.2</v>
       </c>
       <c r="P17">
-        <v>10.53</v>
+        <v>-13.17</v>
       </c>
       <c r="Q17">
-        <v>21.93</v>
+        <v>-25.26</v>
       </c>
       <c r="R17">
-        <v>33.06</v>
+        <v>-36.99</v>
       </c>
       <c r="S17">
-        <v>43.6</v>
+        <v>-47.89</v>
       </c>
       <c r="T17">
-        <v>53.07</v>
+        <v>-58.19</v>
       </c>
       <c r="U17">
-        <v>59.09</v>
+        <v>-67.94</v>
       </c>
       <c r="V17">
-        <v>62.86</v>
+        <v>-77.17</v>
       </c>
       <c r="W17">
-        <v>66.12</v>
+        <v>-85.81</v>
       </c>
       <c r="X17">
-        <v>69.099999999999994</v>
+        <v>-93.55</v>
       </c>
       <c r="Y17">
-        <v>71.92</v>
+        <v>-100.39</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A18">
         <v>170</v>
       </c>
@@ -12915,37 +12915,37 @@
         <v>-0.56999999999999995</v>
       </c>
       <c r="P18">
-        <v>7.39</v>
+        <v>-8.65</v>
       </c>
       <c r="Q18">
-        <v>15.18</v>
+        <v>-16.73</v>
       </c>
       <c r="R18">
-        <v>22.8</v>
+        <v>-24.5</v>
       </c>
       <c r="S18">
-        <v>30.01</v>
+        <v>-31.68</v>
       </c>
       <c r="T18">
-        <v>36.25</v>
+        <v>-38.39</v>
       </c>
       <c r="U18">
-        <v>39.75</v>
+        <v>-44.78</v>
       </c>
       <c r="V18">
-        <v>42.11</v>
+        <v>-50.98</v>
       </c>
       <c r="W18">
-        <v>44.19</v>
+        <v>-56.99</v>
       </c>
       <c r="X18">
-        <v>46.28</v>
+        <v>-62.8</v>
       </c>
       <c r="Y18">
-        <v>48.26</v>
+        <v>-68.27</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A19">
         <v>175</v>
       </c>
@@ -12986,40 +12986,40 @@
         <v>175</v>
       </c>
       <c r="O19">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="P19">
-        <v>3.96</v>
+        <v>-4.22</v>
       </c>
       <c r="Q19">
-        <v>7.92</v>
+        <v>-8.2799999999999994</v>
       </c>
       <c r="R19">
-        <v>11.69</v>
+        <v>-12.08</v>
       </c>
       <c r="S19">
-        <v>15.15</v>
+        <v>-15.5</v>
       </c>
       <c r="T19">
-        <v>18.32</v>
+        <v>-18.88</v>
       </c>
       <c r="U19">
-        <v>19.91</v>
+        <v>-22.13</v>
       </c>
       <c r="V19">
-        <v>20.97</v>
+        <v>-25.2</v>
       </c>
       <c r="W19">
-        <v>22.18</v>
+        <v>-28.17</v>
       </c>
       <c r="X19">
-        <v>23.27</v>
+        <v>-31.07</v>
       </c>
       <c r="Y19">
-        <v>24.29</v>
+        <v>-33.9</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A20">
         <v>180</v>
       </c>
@@ -13063,37 +13063,37 @@
         <v>-0.01</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>-0.01</v>
       </c>
       <c r="Q20">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="R20">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="S20">
-        <v>0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="T20">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="X20">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="Y20">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>3</v>
       </c>
@@ -13128,7 +13128,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A23">
         <v>90</v>
       </c>
@@ -13166,7 +13166,7 @@
         <v>263.44</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A24">
         <v>95</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>261.91000000000003</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A25">
         <v>100</v>
       </c>
@@ -13242,7 +13242,7 @@
         <v>260.39</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A26">
         <v>105</v>
       </c>
@@ -13280,7 +13280,7 @@
         <v>258.88</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A27">
         <v>110</v>
       </c>
@@ -13318,7 +13318,7 @@
         <v>255.29</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A28">
         <v>115</v>
       </c>
@@ -13356,7 +13356,7 @@
         <v>250.66</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A29">
         <v>120</v>
       </c>
@@ -13394,7 +13394,7 @@
         <v>246.07</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A30">
         <v>125</v>
       </c>
@@ -13432,7 +13432,7 @@
         <v>239.41</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A31">
         <v>130</v>
       </c>
@@ -13470,7 +13470,7 @@
         <v>232.33</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.65">
       <c r="A32">
         <v>135</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>220.15</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A33">
         <v>140</v>
       </c>
@@ -13546,7 +13546,7 @@
         <v>209.66</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A34">
         <v>145</v>
       </c>
@@ -13584,7 +13584,7 @@
         <v>196.58</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A35">
         <v>150</v>
       </c>
@@ -13622,7 +13622,7 @@
         <v>180.04</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A36">
         <v>155</v>
       </c>
@@ -13660,7 +13660,7 @@
         <v>159.79</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A37">
         <v>160</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>135.16</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A38">
         <v>165</v>
       </c>
@@ -13736,7 +13736,7 @@
         <v>106.69</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A39">
         <v>170</v>
       </c>
@@ -13774,7 +13774,7 @@
         <v>74.83</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A40">
         <v>175</v>
       </c>
@@ -13812,7 +13812,7 @@
         <v>41.68</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A41">
         <v>180</v>
       </c>
@@ -13860,9 +13860,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.65">
       <c r="A1">
         <v>1.6605200000000001E-2</v>
       </c>
@@ -13881,9 +13881,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:L41"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.7" x14ac:dyDescent="0.65"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A1" s="3" t="s">
         <v>5</v>
       </c>
@@ -13921,729 +13921,729 @@
         <v>340</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A2" s="3">
         <v>90</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>0</v>
       </c>
-      <c r="C2" s="3">
-        <v>27.56</v>
-      </c>
-      <c r="D2" s="3">
-        <v>54.87</v>
-      </c>
-      <c r="E2" s="3">
-        <v>81.72</v>
-      </c>
-      <c r="F2" s="3">
-        <v>107.87</v>
-      </c>
-      <c r="G2" s="3">
-        <v>133.41</v>
-      </c>
-      <c r="H2" s="3">
-        <v>156.19999999999999</v>
-      </c>
-      <c r="I2" s="3">
-        <v>175.43</v>
-      </c>
-      <c r="J2" s="3">
-        <v>193.07</v>
-      </c>
-      <c r="K2" s="3">
-        <v>209.92</v>
-      </c>
-      <c r="L2" s="3">
-        <v>226.44</v>
+      <c r="C2">
+        <v>-25.54</v>
+      </c>
+      <c r="D2">
+        <v>-50.96</v>
+      </c>
+      <c r="E2">
+        <v>-76.709999999999994</v>
+      </c>
+      <c r="F2">
+        <v>-101.98</v>
+      </c>
+      <c r="G2">
+        <v>-127.06</v>
+      </c>
+      <c r="H2">
+        <v>-152.18</v>
+      </c>
+      <c r="I2">
+        <v>-176.19</v>
+      </c>
+      <c r="J2">
+        <v>-197.09</v>
+      </c>
+      <c r="K2">
+        <v>-215.72</v>
+      </c>
+      <c r="L2">
+        <v>-233.32</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A3" s="3">
         <v>95</v>
       </c>
-      <c r="B3" s="3">
-        <v>0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>28</v>
-      </c>
-      <c r="D3" s="3">
-        <v>56.82</v>
-      </c>
-      <c r="E3" s="3">
-        <v>86.03</v>
-      </c>
-      <c r="F3" s="3">
-        <v>114.71</v>
-      </c>
-      <c r="G3" s="3">
-        <v>142.76</v>
-      </c>
-      <c r="H3" s="3">
-        <v>167.41</v>
-      </c>
-      <c r="I3" s="3">
-        <v>188.85</v>
-      </c>
-      <c r="J3" s="3">
-        <v>209.04</v>
-      </c>
-      <c r="K3" s="3">
-        <v>228.49</v>
-      </c>
-      <c r="L3" s="3">
-        <v>247.67</v>
+      <c r="B3">
+        <v>-1.34</v>
+      </c>
+      <c r="C3">
+        <v>-28.17</v>
+      </c>
+      <c r="D3">
+        <v>-56.14</v>
+      </c>
+      <c r="E3">
+        <v>-84.73</v>
+      </c>
+      <c r="F3">
+        <v>-112.39</v>
+      </c>
+      <c r="G3">
+        <v>-139.82</v>
+      </c>
+      <c r="H3">
+        <v>-167.23</v>
+      </c>
+      <c r="I3">
+        <v>-194.36</v>
+      </c>
+      <c r="J3">
+        <v>-220.3</v>
+      </c>
+      <c r="K3">
+        <v>-243.46</v>
+      </c>
+      <c r="L3">
+        <v>-264.51</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A4" s="3">
         <v>100</v>
       </c>
-      <c r="B4" s="3">
-        <v>0</v>
-      </c>
-      <c r="C4" s="3">
-        <v>28.21</v>
-      </c>
-      <c r="D4" s="3">
-        <v>58.28</v>
-      </c>
-      <c r="E4" s="3">
-        <v>89.65</v>
-      </c>
-      <c r="F4" s="3">
-        <v>120.78</v>
-      </c>
-      <c r="G4" s="3">
-        <v>151.27000000000001</v>
-      </c>
-      <c r="H4" s="3">
-        <v>177.9</v>
-      </c>
-      <c r="I4" s="3">
-        <v>201.62</v>
-      </c>
-      <c r="J4" s="3">
-        <v>224.42</v>
-      </c>
-      <c r="K4" s="3">
-        <v>246.73</v>
-      </c>
-      <c r="L4" s="3">
-        <v>268.89999999999998</v>
+      <c r="B4">
+        <v>-1.23</v>
+      </c>
+      <c r="C4">
+        <v>-30.01</v>
+      </c>
+      <c r="D4">
+        <v>-60.97</v>
+      </c>
+      <c r="E4">
+        <v>-92.87</v>
+      </c>
+      <c r="F4">
+        <v>-122.44</v>
+      </c>
+      <c r="G4">
+        <v>-151.05000000000001</v>
+      </c>
+      <c r="H4">
+        <v>-180.15</v>
+      </c>
+      <c r="I4">
+        <v>-209.63</v>
+      </c>
+      <c r="J4">
+        <v>-238.94</v>
+      </c>
+      <c r="K4">
+        <v>-267.12</v>
+      </c>
+      <c r="L4">
+        <v>-293.11</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A5" s="3">
         <v>105</v>
       </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>28.18</v>
-      </c>
-      <c r="D5" s="3">
-        <v>59.21</v>
-      </c>
-      <c r="E5" s="3">
-        <v>92.43</v>
-      </c>
-      <c r="F5" s="3">
-        <v>125.89</v>
-      </c>
-      <c r="G5" s="3">
-        <v>158.79</v>
-      </c>
-      <c r="H5" s="3">
-        <v>187.58</v>
-      </c>
-      <c r="I5" s="3">
-        <v>213.67</v>
-      </c>
-      <c r="J5" s="3">
-        <v>239.15</v>
-      </c>
-      <c r="K5" s="3">
-        <v>264.42</v>
-      </c>
-      <c r="L5" s="3">
-        <v>289.66000000000003</v>
+      <c r="B5">
+        <v>-0.02</v>
+      </c>
+      <c r="C5">
+        <v>-29.61</v>
+      </c>
+      <c r="D5">
+        <v>-62.23</v>
+      </c>
+      <c r="E5">
+        <v>-96.65</v>
+      </c>
+      <c r="F5">
+        <v>-128.83000000000001</v>
+      </c>
+      <c r="G5">
+        <v>-158.46</v>
+      </c>
+      <c r="H5">
+        <v>-188.41</v>
+      </c>
+      <c r="I5">
+        <v>-219.23</v>
+      </c>
+      <c r="J5">
+        <v>-250.54</v>
+      </c>
+      <c r="K5">
+        <v>-281.58</v>
+      </c>
+      <c r="L5">
+        <v>-311.49</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A6" s="3">
         <v>110</v>
       </c>
-      <c r="B6" s="3">
-        <v>0</v>
-      </c>
-      <c r="C6" s="3">
-        <v>27.91</v>
-      </c>
-      <c r="D6" s="3">
-        <v>59.55</v>
-      </c>
-      <c r="E6" s="3">
-        <v>94.2</v>
-      </c>
-      <c r="F6" s="3">
-        <v>129.81</v>
-      </c>
-      <c r="G6" s="3">
-        <v>165.01</v>
-      </c>
-      <c r="H6" s="3">
-        <v>196.06</v>
-      </c>
-      <c r="I6" s="3">
-        <v>224.5</v>
-      </c>
-      <c r="J6" s="3">
-        <v>252.54</v>
-      </c>
-      <c r="K6" s="3">
-        <v>280.64</v>
-      </c>
-      <c r="L6" s="3">
-        <v>308.77</v>
+      <c r="B6">
+        <v>1.1499999999999999</v>
+      </c>
+      <c r="C6">
+        <v>-27.6</v>
+      </c>
+      <c r="D6">
+        <v>-59.99</v>
+      </c>
+      <c r="E6">
+        <v>-95.13</v>
+      </c>
+      <c r="F6">
+        <v>-130.29</v>
+      </c>
+      <c r="G6">
+        <v>-161.63</v>
+      </c>
+      <c r="H6">
+        <v>-192.2</v>
+      </c>
+      <c r="I6">
+        <v>-223.39</v>
+      </c>
+      <c r="J6">
+        <v>-255.4</v>
+      </c>
+      <c r="K6">
+        <v>-287.85000000000002</v>
+      </c>
+      <c r="L6">
+        <v>-319.97000000000003</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A7" s="3">
         <v>115</v>
       </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>27.37</v>
-      </c>
-      <c r="D7" s="3">
-        <v>59.24</v>
-      </c>
-      <c r="E7" s="3">
-        <v>94.82</v>
-      </c>
-      <c r="F7" s="3">
-        <v>132.31</v>
-      </c>
-      <c r="G7" s="3">
-        <v>169.65</v>
-      </c>
-      <c r="H7" s="3">
-        <v>202.96</v>
-      </c>
-      <c r="I7" s="3">
-        <v>233.58</v>
-      </c>
-      <c r="J7" s="3">
-        <v>263.92</v>
-      </c>
-      <c r="K7" s="3">
-        <v>294.57</v>
-      </c>
-      <c r="L7" s="3">
-        <v>325.42</v>
+      <c r="B7">
+        <v>1.22</v>
+      </c>
+      <c r="C7">
+        <v>-26.08</v>
+      </c>
+      <c r="D7">
+        <v>-57.75</v>
+      </c>
+      <c r="E7">
+        <v>-93.23</v>
+      </c>
+      <c r="F7">
+        <v>-130.66999999999999</v>
+      </c>
+      <c r="G7">
+        <v>-165.93</v>
+      </c>
+      <c r="H7">
+        <v>-197.71</v>
+      </c>
+      <c r="I7">
+        <v>-229.12</v>
+      </c>
+      <c r="J7">
+        <v>-261.07</v>
+      </c>
+      <c r="K7">
+        <v>-293.64999999999998</v>
+      </c>
+      <c r="L7">
+        <v>-326.51</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A8" s="3">
         <v>120</v>
       </c>
-      <c r="B8" s="3">
-        <v>0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>26.58</v>
-      </c>
-      <c r="D8" s="3">
-        <v>58.27</v>
-      </c>
-      <c r="E8" s="3">
-        <v>94.21</v>
-      </c>
-      <c r="F8" s="3">
-        <v>133.1</v>
-      </c>
-      <c r="G8" s="3">
-        <v>172.36</v>
-      </c>
-      <c r="H8" s="3">
-        <v>207.95</v>
-      </c>
-      <c r="I8" s="3">
-        <v>240.56</v>
-      </c>
-      <c r="J8" s="3">
-        <v>272.88</v>
-      </c>
-      <c r="K8" s="3">
-        <v>305.68</v>
-      </c>
-      <c r="L8" s="3">
-        <v>338.95</v>
+      <c r="B8">
+        <v>-0.13</v>
+      </c>
+      <c r="C8">
+        <v>-26.56</v>
+      </c>
+      <c r="D8">
+        <v>-58.07</v>
+      </c>
+      <c r="E8">
+        <v>-93.81</v>
+      </c>
+      <c r="F8">
+        <v>-132.51</v>
+      </c>
+      <c r="G8">
+        <v>-171.65</v>
+      </c>
+      <c r="H8">
+        <v>-207.26</v>
+      </c>
+      <c r="I8">
+        <v>-239.86</v>
+      </c>
+      <c r="J8">
+        <v>-272.14999999999998</v>
+      </c>
+      <c r="K8">
+        <v>-304.91000000000003</v>
+      </c>
+      <c r="L8">
+        <v>-338.14</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A9" s="3">
         <v>125</v>
       </c>
-      <c r="B9" s="3">
-        <v>0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>25.52</v>
-      </c>
-      <c r="D9" s="3">
-        <v>56.6</v>
-      </c>
-      <c r="E9" s="3">
-        <v>92.33</v>
-      </c>
-      <c r="F9" s="3">
-        <v>131.82</v>
-      </c>
-      <c r="G9" s="3">
-        <v>172.73</v>
-      </c>
-      <c r="H9" s="3">
-        <v>210.63</v>
-      </c>
-      <c r="I9" s="3">
-        <v>245.05</v>
-      </c>
-      <c r="J9" s="3">
-        <v>279.02</v>
-      </c>
-      <c r="K9" s="3">
-        <v>313.52</v>
-      </c>
-      <c r="L9" s="3">
-        <v>348.7</v>
+      <c r="B9">
+        <v>-1.45</v>
+      </c>
+      <c r="C9">
+        <v>-27.73</v>
+      </c>
+      <c r="D9">
+        <v>-59.48</v>
+      </c>
+      <c r="E9">
+        <v>-96.31</v>
+      </c>
+      <c r="F9">
+        <v>-136.38</v>
+      </c>
+      <c r="G9">
+        <v>-177.06</v>
+      </c>
+      <c r="H9">
+        <v>-217.25</v>
+      </c>
+      <c r="I9">
+        <v>-253.7</v>
+      </c>
+      <c r="J9">
+        <v>-287.47000000000003</v>
+      </c>
+      <c r="K9">
+        <v>-320.92</v>
+      </c>
+      <c r="L9">
+        <v>-354.75</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A10" s="3">
         <v>130</v>
       </c>
-      <c r="B10" s="3">
-        <v>0</v>
-      </c>
-      <c r="C10" s="3">
-        <v>24.2</v>
-      </c>
-      <c r="D10" s="3">
-        <v>54.24</v>
-      </c>
-      <c r="E10" s="3">
-        <v>89.16</v>
-      </c>
-      <c r="F10" s="3">
-        <v>128.33000000000001</v>
-      </c>
-      <c r="G10" s="3">
-        <v>170.19</v>
-      </c>
-      <c r="H10" s="3">
-        <v>210.41</v>
-      </c>
-      <c r="I10" s="3">
-        <v>246.58</v>
-      </c>
-      <c r="J10" s="3">
-        <v>281.93</v>
-      </c>
-      <c r="K10" s="3">
-        <v>317.7</v>
-      </c>
-      <c r="L10" s="3">
-        <v>354.22</v>
+      <c r="B10">
+        <v>-1.38</v>
+      </c>
+      <c r="C10">
+        <v>-27.2</v>
+      </c>
+      <c r="D10">
+        <v>-58.44</v>
+      </c>
+      <c r="E10">
+        <v>-94.94</v>
+      </c>
+      <c r="F10">
+        <v>-135.94</v>
+      </c>
+      <c r="G10">
+        <v>-178.16</v>
+      </c>
+      <c r="H10">
+        <v>-219.48</v>
+      </c>
+      <c r="I10">
+        <v>-260.17</v>
+      </c>
+      <c r="J10">
+        <v>-297.49</v>
+      </c>
+      <c r="K10">
+        <v>-332.66</v>
+      </c>
+      <c r="L10">
+        <v>-367.54</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A11" s="3">
         <v>135</v>
       </c>
-      <c r="B11" s="3">
-        <v>0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>22.62</v>
-      </c>
-      <c r="D11" s="3">
-        <v>51.18</v>
-      </c>
-      <c r="E11" s="3">
-        <v>84.7</v>
-      </c>
-      <c r="F11" s="3">
-        <v>122.68</v>
-      </c>
-      <c r="G11" s="3">
-        <v>164.19</v>
-      </c>
-      <c r="H11" s="3">
-        <v>206.21</v>
-      </c>
-      <c r="I11" s="3">
-        <v>244.31</v>
-      </c>
-      <c r="J11" s="3">
-        <v>280.93</v>
-      </c>
-      <c r="K11" s="3">
-        <v>317.64999999999998</v>
-      </c>
-      <c r="L11" s="3">
-        <v>355.03</v>
+      <c r="B11">
+        <v>-0.2</v>
+      </c>
+      <c r="C11">
+        <v>-23.92</v>
+      </c>
+      <c r="D11">
+        <v>-53.25</v>
+      </c>
+      <c r="E11">
+        <v>-87.76</v>
+      </c>
+      <c r="F11">
+        <v>-127.29</v>
+      </c>
+      <c r="G11">
+        <v>-170.11</v>
+      </c>
+      <c r="H11">
+        <v>-212.97</v>
+      </c>
+      <c r="I11">
+        <v>-254.93</v>
+      </c>
+      <c r="J11">
+        <v>-296.05</v>
+      </c>
+      <c r="K11">
+        <v>-333.92</v>
+      </c>
+      <c r="L11">
+        <v>-369.88</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A12" s="3">
         <v>140</v>
       </c>
-      <c r="B12" s="3">
-        <v>0</v>
-      </c>
-      <c r="C12" s="3">
-        <v>20.8</v>
-      </c>
-      <c r="D12" s="3">
-        <v>47.44</v>
-      </c>
-      <c r="E12" s="3">
-        <v>78.98</v>
-      </c>
-      <c r="F12" s="3">
-        <v>114.96</v>
-      </c>
-      <c r="G12" s="3">
-        <v>154.85</v>
-      </c>
-      <c r="H12" s="3">
-        <v>196.81</v>
-      </c>
-      <c r="I12" s="3">
-        <v>236.57</v>
-      </c>
-      <c r="J12" s="3">
-        <v>274.45999999999998</v>
-      </c>
-      <c r="K12" s="3">
-        <v>312.01</v>
-      </c>
-      <c r="L12" s="3">
-        <v>349.92</v>
+      <c r="B12">
+        <v>0.98</v>
+      </c>
+      <c r="C12">
+        <v>-19.68</v>
+      </c>
+      <c r="D12">
+        <v>-46.03</v>
+      </c>
+      <c r="E12">
+        <v>-77.52</v>
+      </c>
+      <c r="F12">
+        <v>-113.63</v>
+      </c>
+      <c r="G12">
+        <v>-153.63</v>
+      </c>
+      <c r="H12">
+        <v>-195.73</v>
+      </c>
+      <c r="I12">
+        <v>-238.41</v>
+      </c>
+      <c r="J12">
+        <v>-280.16000000000003</v>
+      </c>
+      <c r="K12">
+        <v>-320.52</v>
+      </c>
+      <c r="L12">
+        <v>-357.55</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A13" s="3">
         <v>145</v>
       </c>
-      <c r="B13" s="3">
-        <v>0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>18.75</v>
-      </c>
-      <c r="D13" s="3">
-        <v>43.08</v>
-      </c>
-      <c r="E13" s="3">
-        <v>72.06</v>
-      </c>
-      <c r="F13" s="3">
-        <v>105.28</v>
-      </c>
-      <c r="G13" s="3">
-        <v>142.41999999999999</v>
-      </c>
-      <c r="H13" s="3">
-        <v>182.5</v>
-      </c>
-      <c r="I13" s="3">
-        <v>222.48</v>
-      </c>
-      <c r="J13" s="3">
-        <v>260.23</v>
-      </c>
-      <c r="K13" s="3">
-        <v>297.8</v>
-      </c>
-      <c r="L13" s="3">
-        <v>335.92</v>
+      <c r="B13">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="C13">
+        <v>-16.57</v>
+      </c>
+      <c r="D13">
+        <v>-39.24</v>
+      </c>
+      <c r="E13">
+        <v>-66.47</v>
+      </c>
+      <c r="F13">
+        <v>-97.73</v>
+      </c>
+      <c r="G13">
+        <v>-132.71</v>
+      </c>
+      <c r="H13">
+        <v>-170.68</v>
+      </c>
+      <c r="I13">
+        <v>-210.48</v>
+      </c>
+      <c r="J13">
+        <v>-251.52</v>
+      </c>
+      <c r="K13">
+        <v>-292.23</v>
+      </c>
+      <c r="L13">
+        <v>-331.09</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A14" s="3">
         <v>150</v>
       </c>
-      <c r="B14" s="3">
-        <v>0</v>
-      </c>
-      <c r="C14" s="3">
-        <v>16.489999999999998</v>
-      </c>
-      <c r="D14" s="3">
-        <v>38.119999999999997</v>
-      </c>
-      <c r="E14" s="3">
-        <v>64.02</v>
-      </c>
-      <c r="F14" s="3">
-        <v>93.77</v>
-      </c>
-      <c r="G14" s="3">
-        <v>127.21</v>
-      </c>
-      <c r="H14" s="3">
-        <v>163.78</v>
-      </c>
-      <c r="I14" s="3">
-        <v>202.06</v>
-      </c>
-      <c r="J14" s="3">
-        <v>238.79</v>
-      </c>
-      <c r="K14" s="3">
-        <v>274.49</v>
-      </c>
-      <c r="L14" s="3">
-        <v>310.44</v>
+      <c r="B14">
+        <v>-0.14000000000000001</v>
+      </c>
+      <c r="C14">
+        <v>-15.25</v>
+      </c>
+      <c r="D14">
+        <v>-34.76</v>
+      </c>
+      <c r="E14">
+        <v>-58.33</v>
+      </c>
+      <c r="F14">
+        <v>-85.34</v>
+      </c>
+      <c r="G14">
+        <v>-115.71</v>
+      </c>
+      <c r="H14">
+        <v>-148.94</v>
+      </c>
+      <c r="I14">
+        <v>-184.34</v>
+      </c>
+      <c r="J14">
+        <v>-221.3</v>
+      </c>
+      <c r="K14">
+        <v>-259.51</v>
+      </c>
+      <c r="L14">
+        <v>-298.55</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A15" s="3">
         <v>155</v>
       </c>
-      <c r="B15" s="3">
-        <v>0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>14.05</v>
-      </c>
-      <c r="D15" s="3">
-        <v>32.630000000000003</v>
-      </c>
-      <c r="E15" s="3">
-        <v>54.98</v>
-      </c>
-      <c r="F15" s="3">
-        <v>80.64</v>
-      </c>
-      <c r="G15" s="3">
-        <v>109.53</v>
-      </c>
-      <c r="H15" s="3">
-        <v>141.37</v>
-      </c>
-      <c r="I15" s="3">
-        <v>175.58</v>
-      </c>
-      <c r="J15" s="3">
-        <v>210.49</v>
-      </c>
-      <c r="K15" s="3">
-        <v>243.81</v>
-      </c>
-      <c r="L15" s="3">
-        <v>276.62</v>
+      <c r="B15">
+        <v>-1.39</v>
+      </c>
+      <c r="C15">
+        <v>-14.25</v>
+      </c>
+      <c r="D15">
+        <v>-30.91</v>
+      </c>
+      <c r="E15">
+        <v>-51.26</v>
+      </c>
+      <c r="F15">
+        <v>-75.069999999999993</v>
+      </c>
+      <c r="G15">
+        <v>-101.61</v>
+      </c>
+      <c r="H15">
+        <v>-130.55000000000001</v>
+      </c>
+      <c r="I15">
+        <v>-161.1</v>
+      </c>
+      <c r="J15">
+        <v>-193.22</v>
+      </c>
+      <c r="K15">
+        <v>-226.65</v>
+      </c>
+      <c r="L15">
+        <v>-261.26</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A16" s="3">
         <v>160</v>
       </c>
-      <c r="B16" s="3">
-        <v>0</v>
-      </c>
-      <c r="C16" s="3">
-        <v>11.44</v>
-      </c>
-      <c r="D16" s="3">
-        <v>26.69</v>
-      </c>
-      <c r="E16" s="3">
-        <v>45.08</v>
-      </c>
-      <c r="F16" s="3">
-        <v>66.13</v>
-      </c>
-      <c r="G16" s="3">
-        <v>89.85</v>
-      </c>
-      <c r="H16" s="3">
-        <v>116.17</v>
-      </c>
-      <c r="I16" s="3">
-        <v>144.83000000000001</v>
-      </c>
-      <c r="J16" s="3">
-        <v>175.19</v>
-      </c>
-      <c r="K16" s="3">
-        <v>205.75</v>
-      </c>
-      <c r="L16" s="3">
-        <v>234.92</v>
+      <c r="B16">
+        <v>-1.24</v>
+      </c>
+      <c r="C16">
+        <v>-12.17</v>
+      </c>
+      <c r="D16">
+        <v>-26.18</v>
+      </c>
+      <c r="E16">
+        <v>-43.22</v>
+      </c>
+      <c r="F16">
+        <v>-63.33</v>
+      </c>
+      <c r="G16">
+        <v>-86.41</v>
+      </c>
+      <c r="H16">
+        <v>-111.85</v>
+      </c>
+      <c r="I16">
+        <v>-138.57</v>
+      </c>
+      <c r="J16">
+        <v>-165.94</v>
+      </c>
+      <c r="K16">
+        <v>-194.4</v>
+      </c>
+      <c r="L16">
+        <v>-223.81</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A17" s="3">
         <v>165</v>
       </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>8.6999999999999993</v>
-      </c>
-      <c r="D17" s="3">
-        <v>20.36</v>
-      </c>
-      <c r="E17" s="3">
-        <v>34.47</v>
-      </c>
-      <c r="F17" s="3">
-        <v>50.53</v>
-      </c>
-      <c r="G17" s="3">
-        <v>68.73</v>
-      </c>
-      <c r="H17" s="3">
-        <v>88.98</v>
-      </c>
-      <c r="I17" s="3">
-        <v>111.06</v>
-      </c>
-      <c r="J17" s="3">
-        <v>134.78</v>
-      </c>
-      <c r="K17" s="3">
-        <v>159.77000000000001</v>
-      </c>
-      <c r="L17" s="3">
-        <v>184.97</v>
+      <c r="B17">
+        <v>-0.01</v>
+      </c>
+      <c r="C17">
+        <v>-8.3699999999999992</v>
+      </c>
+      <c r="D17">
+        <v>-19.510000000000002</v>
+      </c>
+      <c r="E17">
+        <v>-33.340000000000003</v>
+      </c>
+      <c r="F17">
+        <v>-49.61</v>
+      </c>
+      <c r="G17">
+        <v>-68.37</v>
+      </c>
+      <c r="H17">
+        <v>-89.44</v>
+      </c>
+      <c r="I17">
+        <v>-112.38</v>
+      </c>
+      <c r="J17">
+        <v>-136.61000000000001</v>
+      </c>
+      <c r="K17">
+        <v>-161.12</v>
+      </c>
+      <c r="L17">
+        <v>-185.61</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A18" s="3">
         <v>170</v>
       </c>
-      <c r="B18" s="3">
-        <v>0</v>
-      </c>
-      <c r="C18" s="3">
-        <v>5.85</v>
-      </c>
-      <c r="D18" s="3">
-        <v>13.74</v>
-      </c>
-      <c r="E18" s="3">
-        <v>23.3</v>
-      </c>
-      <c r="F18" s="3">
-        <v>34.130000000000003</v>
-      </c>
-      <c r="G18" s="3">
-        <v>46.53</v>
-      </c>
-      <c r="H18" s="3">
-        <v>60.27</v>
-      </c>
-      <c r="I18" s="3">
-        <v>75.239999999999995</v>
-      </c>
-      <c r="J18" s="3">
-        <v>91.36</v>
-      </c>
-      <c r="K18" s="3">
-        <v>108.52</v>
-      </c>
-      <c r="L18" s="3">
-        <v>126.54</v>
+      <c r="B18">
+        <v>1.23</v>
+      </c>
+      <c r="C18">
+        <v>-3.95</v>
+      </c>
+      <c r="D18">
+        <v>-11.32</v>
+      </c>
+      <c r="E18">
+        <v>-20.94</v>
+      </c>
+      <c r="F18">
+        <v>-32.64</v>
+      </c>
+      <c r="G18">
+        <v>-46</v>
+      </c>
+      <c r="H18">
+        <v>-61.04</v>
+      </c>
+      <c r="I18">
+        <v>-77.87</v>
+      </c>
+      <c r="J18">
+        <v>-95.91</v>
+      </c>
+      <c r="K18">
+        <v>-114.78</v>
+      </c>
+      <c r="L18">
+        <v>-134.16</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A19" s="3">
         <v>175</v>
       </c>
-      <c r="B19" s="3">
-        <v>0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>2.94</v>
-      </c>
-      <c r="D19" s="3">
-        <v>6.91</v>
-      </c>
-      <c r="E19" s="3">
-        <v>11.74</v>
-      </c>
-      <c r="F19" s="3">
-        <v>17.21</v>
-      </c>
-      <c r="G19" s="3">
-        <v>23.51</v>
-      </c>
-      <c r="H19" s="3">
-        <v>30.48</v>
-      </c>
-      <c r="I19" s="3">
-        <v>38.03</v>
-      </c>
-      <c r="J19" s="3">
-        <v>46.12</v>
-      </c>
-      <c r="K19" s="3">
-        <v>54.73</v>
-      </c>
-      <c r="L19" s="3">
-        <v>63.83</v>
+      <c r="B19">
+        <v>1.35</v>
+      </c>
+      <c r="C19">
+        <v>-0.99</v>
+      </c>
+      <c r="D19">
+        <v>-4.54</v>
+      </c>
+      <c r="E19">
+        <v>-9.18</v>
+      </c>
+      <c r="F19">
+        <v>-14.79</v>
+      </c>
+      <c r="G19">
+        <v>-21.77</v>
+      </c>
+      <c r="H19">
+        <v>-29.75</v>
+      </c>
+      <c r="I19">
+        <v>-38.36</v>
+      </c>
+      <c r="J19">
+        <v>-47.54</v>
+      </c>
+      <c r="K19">
+        <v>-57.24</v>
+      </c>
+      <c r="L19">
+        <v>-67.19</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A20" s="3">
         <v>180</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
+        <v>-0.01</v>
+      </c>
+      <c r="C20">
         <v>0</v>
       </c>
-      <c r="C20" s="3">
-        <v>0</v>
-      </c>
-      <c r="D20" s="3">
+      <c r="D20">
         <v>-0.01</v>
       </c>
-      <c r="E20" s="3">
-        <v>-0.02</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-0.02</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-0.02</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="E20">
+        <v>-0.01</v>
+      </c>
+      <c r="F20">
+        <v>-0.01</v>
+      </c>
+      <c r="G20">
         <v>-0.03</v>
       </c>
-      <c r="I20" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="J20" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-0.03</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-0.05</v>
+      <c r="H20">
+        <v>-0.04</v>
+      </c>
+      <c r="I20">
+        <v>-0.06</v>
+      </c>
+      <c r="J20">
+        <v>-0.06</v>
+      </c>
+      <c r="K20">
+        <v>-7.0000000000000007E-2</v>
+      </c>
+      <c r="L20">
+        <v>-7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A22" t="s">
         <v>4</v>
       </c>
@@ -14681,7 +14681,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A23">
         <v>90</v>
       </c>
@@ -14719,7 +14719,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A24">
         <v>95</v>
       </c>
@@ -14757,7 +14757,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A25">
         <v>100</v>
       </c>
@@ -14795,7 +14795,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A26">
         <v>105</v>
       </c>
@@ -14833,7 +14833,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A27">
         <v>110</v>
       </c>
@@ -14871,7 +14871,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A28">
         <v>115</v>
       </c>
@@ -14909,7 +14909,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A29">
         <v>120</v>
       </c>
@@ -14947,7 +14947,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A30">
         <v>125</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A31">
         <v>130</v>
       </c>
@@ -15023,7 +15023,7 @@
         <v>360.6</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A32">
         <v>135</v>
       </c>
@@ -15061,7 +15061,7 @@
         <v>361.4</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A33">
         <v>140</v>
       </c>
@@ -15099,7 +15099,7 @@
         <v>354.8</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A34">
         <v>145</v>
       </c>
@@ -15137,7 +15137,7 @@
         <v>340.1</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A35">
         <v>150</v>
       </c>
@@ -15175,7 +15175,7 @@
         <v>317.10000000000002</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A36">
         <v>155</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>284.3</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A37">
         <v>160</v>
       </c>
@@ -15251,7 +15251,7 @@
         <v>243.1</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A38">
         <v>165</v>
       </c>
@@ -15289,7 +15289,7 @@
         <v>192.4</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A39">
         <v>170</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>133.4</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A40">
         <v>175</v>
       </c>
@@ -15365,7 +15365,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.65">
       <c r="A41">
         <v>180</v>
       </c>
